--- a/platform_PiN_output/Somalia___SOM/PiN_step2_Somalia___SOM_1022_08AM.xlsx
+++ b/platform_PiN_output/Somalia___SOM/PiN_step2_Somalia___SOM_1022_08AM.xlsx
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>4614117</v>
+        <v>4080650</v>
       </c>
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="10" t="n"/>
@@ -769,37 +769,37 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>7587379</v>
+        <v>6888389</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>38.9</v>
+        <v>40.8</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>2950272</v>
+        <v>2807246</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>56.3</v>
+        <v>52.4</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>4271939</v>
+        <v>3606447</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>233633</v>
+        <v>368091</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="R6" s="9" t="n">
-        <v>108545</v>
+        <v>106113</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>60.8</v>
+        <v>59.2</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>4614117</v>
+        <v>4080650</v>
       </c>
     </row>
     <row r="7">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>4048865</v>
+        <v>4080650</v>
       </c>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
@@ -834,34 +834,34 @@
         <v>6888389</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>41.2</v>
+        <v>40.8</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>2839280</v>
+        <v>2807246</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>54</v>
+        <v>52.4</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>3722050</v>
+        <v>3606447</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="P7" s="11" t="n">
-        <v>219809</v>
+        <v>368091</v>
       </c>
       <c r="Q7" s="11" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="R7" s="11" t="n">
-        <v>107005</v>
+        <v>106113</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>58.8</v>
+        <v>59.2</v>
       </c>
       <c r="T7" s="11" t="n">
-        <v>4048865</v>
+        <v>4080650</v>
       </c>
     </row>
     <row r="8">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>565252</v>
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
@@ -893,37 +893,37 @@
         </is>
       </c>
       <c r="J8" s="11" t="n">
-        <v>698990</v>
+        <v>0</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>15.9</v>
+        <v/>
       </c>
       <c r="L8" s="11" t="n">
-        <v>110993</v>
+        <v>0</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>78.7</v>
+        <v/>
       </c>
       <c r="N8" s="11" t="n">
-        <v>549888</v>
+        <v>0</v>
       </c>
       <c r="O8" s="11" t="n">
-        <v>2</v>
+        <v/>
       </c>
       <c r="P8" s="11" t="n">
-        <v>13824</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="11" t="n">
-        <v>0.2</v>
+        <v/>
       </c>
       <c r="R8" s="11" t="n">
-        <v>1540</v>
+        <v>0</v>
       </c>
       <c r="S8" s="11" t="n">
-        <v>80.90000000000001</v>
+        <v/>
       </c>
       <c r="T8" s="11" t="n">
-        <v>565252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>2214776</v>
+        <v>1958712</v>
       </c>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>2399341</v>
+        <v>2121938</v>
       </c>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="E11" s="13" t="n">
-        <v>354932</v>
+        <v>313896</v>
       </c>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="E12" s="13" t="n">
-        <v>461412</v>
+        <v>408065</v>
       </c>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
@@ -1276,37 +1276,37 @@
         </is>
       </c>
       <c r="F8" s="22" t="n">
-        <v>41996</v>
+        <v>41675</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>40.8</v>
       </c>
       <c r="H8" s="23" t="n">
-        <v>17114</v>
+        <v>17003</v>
       </c>
       <c r="I8" s="24" t="n">
-        <v>53.9</v>
+        <v>51.9</v>
       </c>
       <c r="J8" s="24" t="n">
-        <v>22618</v>
+        <v>21629</v>
       </c>
       <c r="K8" s="25" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="L8" s="25" t="n">
-        <v>1679</v>
+        <v>2459</v>
       </c>
       <c r="M8" s="26" t="n">
         <v>1.4</v>
       </c>
       <c r="N8" s="26" t="n">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="O8" s="27" t="n">
         <v>59.2</v>
       </c>
       <c r="P8" s="27" t="n">
-        <v>24882</v>
+        <v>24672</v>
       </c>
       <c r="Q8" s="28" t="inlineStr">
         <is>
@@ -1334,16 +1334,16 @@
         <v>14315</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>59.1</v>
+        <v>53.5</v>
       </c>
       <c r="J9" s="24" t="n">
-        <v>22381</v>
+        <v>20260</v>
       </c>
       <c r="K9" s="25" t="n">
-        <v>3.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L9" s="25" t="n">
-        <v>1174</v>
+        <v>3295</v>
       </c>
       <c r="M9" s="26" t="n">
         <v>0</v>
@@ -1423,25 +1423,25 @@
         </is>
       </c>
       <c r="F11" s="22" t="n">
-        <v>88228</v>
+        <v>87920</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>82.8</v>
       </c>
       <c r="H11" s="23" t="n">
-        <v>73045</v>
+        <v>72798</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>14032</v>
+        <v>13188</v>
       </c>
       <c r="K11" s="25" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="L11" s="25" t="n">
-        <v>887</v>
+        <v>1670</v>
       </c>
       <c r="M11" s="26" t="n">
         <v>0.3</v>
@@ -1453,7 +1453,7 @@
         <v>17.2</v>
       </c>
       <c r="P11" s="27" t="n">
-        <v>15183</v>
+        <v>15122</v>
       </c>
       <c r="Q11" s="28" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
         <v>24451</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>47.2</v>
+        <v>42.9</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>26902</v>
+        <v>24451</v>
       </c>
       <c r="K12" s="25" t="n">
-        <v>9.800000000000001</v>
+        <v>14.2</v>
       </c>
       <c r="L12" s="25" t="n">
-        <v>5586</v>
+        <v>8093</v>
       </c>
       <c r="M12" s="26" t="n">
         <v>0</v>
@@ -1499,10 +1499,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="27" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
       <c r="P12" s="27" t="n">
-        <v>32487</v>
+        <v>32544</v>
       </c>
       <c r="Q12" s="28" t="inlineStr">
         <is>
@@ -1521,37 +1521,37 @@
         </is>
       </c>
       <c r="F13" s="22" t="n">
-        <v>144108</v>
+        <v>127135</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>31907</v>
+        <v>28224</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>75.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>108513</v>
+        <v>95478</v>
       </c>
       <c r="K13" s="25" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="L13" s="25" t="n">
-        <v>3619</v>
+        <v>3433</v>
       </c>
       <c r="M13" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="26" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="O13" s="27" t="n">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="P13" s="27" t="n">
-        <v>112201</v>
+        <v>98911</v>
       </c>
       <c r="Q13" s="28" t="inlineStr">
         <is>
@@ -1570,37 +1570,37 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>101067</v>
+        <v>91075</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>41.4</v>
+        <v>41.8</v>
       </c>
       <c r="H14" s="23" t="n">
-        <v>41856</v>
+        <v>38069</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>55.9</v>
+        <v>53.8</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>56519</v>
+        <v>48998</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="L14" s="25" t="n">
-        <v>1354</v>
+        <v>3279</v>
       </c>
       <c r="M14" s="26" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="N14" s="26" t="n">
-        <v>1328</v>
+        <v>729</v>
       </c>
       <c r="O14" s="27" t="n">
-        <v>58.6</v>
+        <v>58.2</v>
       </c>
       <c r="P14" s="27" t="n">
-        <v>59200</v>
+        <v>53006</v>
       </c>
       <c r="Q14" s="28" t="inlineStr">
         <is>
@@ -1677,16 +1677,16 @@
         <v>20574</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>73.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>59211</v>
+        <v>57105</v>
       </c>
       <c r="K16" s="25" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="L16" s="25" t="n">
-        <v>1296</v>
+        <v>3321</v>
       </c>
       <c r="M16" s="26" t="n">
         <v>0</v>
@@ -1695,10 +1695,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="27" t="n">
-        <v>74.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="P16" s="27" t="n">
-        <v>60507</v>
+        <v>60426</v>
       </c>
       <c r="Q16" s="28" t="inlineStr">
         <is>
@@ -1717,37 +1717,37 @@
         </is>
       </c>
       <c r="F17" s="22" t="n">
-        <v>387167</v>
+        <v>361685</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>41.2</v>
+        <v>42</v>
       </c>
       <c r="H17" s="23" t="n">
-        <v>159399</v>
+        <v>151908</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>58.2</v>
+        <v>57.4</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>225215</v>
+        <v>207607</v>
       </c>
       <c r="K17" s="25" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="25" t="n">
-        <v>331</v>
+        <v>0</v>
       </c>
       <c r="M17" s="26" t="n">
         <v>0.6</v>
       </c>
       <c r="N17" s="26" t="n">
-        <v>2247</v>
+        <v>2170</v>
       </c>
       <c r="O17" s="27" t="n">
-        <v>58.8</v>
+        <v>58</v>
       </c>
       <c r="P17" s="27" t="n">
-        <v>227793</v>
+        <v>209777</v>
       </c>
       <c r="Q17" s="28" t="inlineStr">
         <is>
@@ -1818,22 +1818,22 @@
         <v>43330</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>92</v>
+        <v>56.1</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>39871</v>
+        <v>24308</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>7.8</v>
+        <v>40.9</v>
       </c>
       <c r="J19" s="24" t="n">
-        <v>3398</v>
+        <v>17722</v>
       </c>
       <c r="K19" s="25" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="L19" s="25" t="n">
-        <v>61</v>
+        <v>1300</v>
       </c>
       <c r="M19" s="26" t="n">
         <v>0</v>
@@ -1842,14 +1842,14 @@
         <v>0</v>
       </c>
       <c r="O19" s="27" t="n">
-        <v>8</v>
+        <v>43.9</v>
       </c>
       <c r="P19" s="27" t="n">
-        <v>3459</v>
+        <v>19022</v>
       </c>
       <c r="Q19" s="28" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         <v>12388</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="J20" s="24" t="n">
-        <v>15767</v>
+        <v>13233</v>
       </c>
       <c r="K20" s="25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L20" s="25" t="n">
-        <v>0</v>
+        <v>2534</v>
       </c>
       <c r="M20" s="26" t="n">
         <v>0</v>
@@ -1913,37 +1913,37 @@
         </is>
       </c>
       <c r="F21" s="22" t="n">
-        <v>77324</v>
+        <v>76115</v>
       </c>
       <c r="G21" s="23" t="n">
-        <v>39.6</v>
+        <v>35.2</v>
       </c>
       <c r="H21" s="23" t="n">
-        <v>30656</v>
+        <v>26792</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>59.3</v>
+        <v>59.7</v>
       </c>
       <c r="J21" s="24" t="n">
-        <v>45878</v>
+        <v>45441</v>
       </c>
       <c r="K21" s="25" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="L21" s="25" t="n">
-        <v>412</v>
+        <v>2892</v>
       </c>
       <c r="M21" s="26" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="N21" s="26" t="n">
-        <v>378</v>
+        <v>989</v>
       </c>
       <c r="O21" s="27" t="n">
-        <v>60.4</v>
+        <v>64.8</v>
       </c>
       <c r="P21" s="27" t="n">
-        <v>46667</v>
+        <v>49323</v>
       </c>
       <c r="Q21" s="28" t="inlineStr">
         <is>
@@ -1962,37 +1962,37 @@
         </is>
       </c>
       <c r="F22" s="22" t="n">
-        <v>158041</v>
+        <v>157610</v>
       </c>
       <c r="G22" s="23" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="H22" s="23" t="n">
-        <v>84732</v>
+        <v>84637</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>45.4</v>
+        <v>44.8</v>
       </c>
       <c r="J22" s="24" t="n">
-        <v>71727</v>
+        <v>70609</v>
       </c>
       <c r="K22" s="25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L22" s="25" t="n">
-        <v>3</v>
+        <v>788</v>
       </c>
       <c r="M22" s="26" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="26" t="n">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="O22" s="27" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="P22" s="27" t="n">
-        <v>73309</v>
+        <v>72973</v>
       </c>
       <c r="Q22" s="28" t="inlineStr">
         <is>
@@ -2014,16 +2014,16 @@
         <v>60130</v>
       </c>
       <c r="G23" s="23" t="n">
-        <v>96.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H23" s="23" t="n">
-        <v>57899</v>
+        <v>58095</v>
       </c>
       <c r="I23" s="24" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="J23" s="24" t="n">
-        <v>2231</v>
+        <v>2035</v>
       </c>
       <c r="K23" s="25" t="n">
         <v>0</v>
@@ -2038,10 +2038,10 @@
         <v>0</v>
       </c>
       <c r="O23" s="27" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P23" s="27" t="n">
-        <v>2231</v>
+        <v>2035</v>
       </c>
       <c r="Q23" s="28" t="inlineStr">
         <is>
@@ -2069,16 +2069,16 @@
         <v>238260</v>
       </c>
       <c r="I24" s="24" t="n">
-        <v>41.1</v>
+        <v>38.6</v>
       </c>
       <c r="J24" s="24" t="n">
-        <v>193528</v>
+        <v>181756</v>
       </c>
       <c r="K24" s="25" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="L24" s="25" t="n">
-        <v>15539</v>
+        <v>27310</v>
       </c>
       <c r="M24" s="26" t="n">
         <v>5</v>
@@ -2118,16 +2118,16 @@
         <v>63667</v>
       </c>
       <c r="I25" s="24" t="n">
-        <v>28.4</v>
+        <v>26.4</v>
       </c>
       <c r="J25" s="24" t="n">
-        <v>25611</v>
+        <v>23808</v>
       </c>
       <c r="K25" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L25" s="25" t="n">
-        <v>902</v>
+        <v>2705</v>
       </c>
       <c r="M25" s="26" t="n">
         <v>0</v>
@@ -2210,22 +2210,22 @@
         <v>107255</v>
       </c>
       <c r="G27" s="23" t="n">
-        <v>27</v>
+        <v>21.2</v>
       </c>
       <c r="H27" s="23" t="n">
-        <v>29000</v>
+        <v>22739</v>
       </c>
       <c r="I27" s="24" t="n">
-        <v>56.1</v>
+        <v>42.2</v>
       </c>
       <c r="J27" s="24" t="n">
-        <v>60166</v>
+        <v>45241</v>
       </c>
       <c r="K27" s="25" t="n">
-        <v>16.9</v>
+        <v>36.6</v>
       </c>
       <c r="L27" s="25" t="n">
-        <v>18088</v>
+        <v>39275</v>
       </c>
       <c r="M27" s="26" t="n">
         <v>0</v>
@@ -2234,14 +2234,14 @@
         <v>0</v>
       </c>
       <c r="O27" s="27" t="n">
-        <v>73</v>
+        <v>78.8</v>
       </c>
       <c r="P27" s="27" t="n">
-        <v>78255</v>
+        <v>84516</v>
       </c>
       <c r="Q27" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2256,25 +2256,25 @@
         </is>
       </c>
       <c r="F28" s="22" t="n">
-        <v>156199</v>
+        <v>153220</v>
       </c>
       <c r="G28" s="23" t="n">
-        <v>25.6</v>
+        <v>25.2</v>
       </c>
       <c r="H28" s="23" t="n">
-        <v>39919</v>
+        <v>38611</v>
       </c>
       <c r="I28" s="24" t="n">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
       <c r="J28" s="24" t="n">
-        <v>93590</v>
+        <v>91626</v>
       </c>
       <c r="K28" s="25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="L28" s="25" t="n">
-        <v>22690</v>
+        <v>22983</v>
       </c>
       <c r="M28" s="26" t="n">
         <v>0</v>
@@ -2283,10 +2283,10 @@
         <v>0</v>
       </c>
       <c r="O28" s="27" t="n">
-        <v>74.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="P28" s="27" t="n">
-        <v>116280</v>
+        <v>114609</v>
       </c>
       <c r="Q28" s="28" t="inlineStr">
         <is>
@@ -2305,37 +2305,37 @@
         </is>
       </c>
       <c r="F29" s="22" t="n">
-        <v>132406</v>
+        <v>123115</v>
       </c>
       <c r="G29" s="23" t="n">
-        <v>45.4</v>
+        <v>45.8</v>
       </c>
       <c r="H29" s="23" t="n">
-        <v>60140</v>
+        <v>56387</v>
       </c>
       <c r="I29" s="24" t="n">
-        <v>52.9</v>
+        <v>51.4</v>
       </c>
       <c r="J29" s="24" t="n">
-        <v>70005</v>
+        <v>63281</v>
       </c>
       <c r="K29" s="25" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="L29" s="25" t="n">
-        <v>1863</v>
+        <v>3078</v>
       </c>
       <c r="M29" s="26" t="n">
         <v>0.4</v>
       </c>
       <c r="N29" s="26" t="n">
-        <v>530</v>
+        <v>492</v>
       </c>
       <c r="O29" s="27" t="n">
-        <v>54.7</v>
+        <v>54.3</v>
       </c>
       <c r="P29" s="27" t="n">
-        <v>72398</v>
+        <v>66851</v>
       </c>
       <c r="Q29" s="28" t="inlineStr">
         <is>
@@ -2354,37 +2354,37 @@
         </is>
       </c>
       <c r="F30" s="22" t="n">
-        <v>81689</v>
+        <v>81395</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>35.9</v>
       </c>
       <c r="H30" s="23" t="n">
-        <v>29363</v>
+        <v>29221</v>
       </c>
       <c r="I30" s="24" t="n">
-        <v>62.5</v>
+        <v>61.1</v>
       </c>
       <c r="J30" s="24" t="n">
-        <v>51017</v>
+        <v>49732</v>
       </c>
       <c r="K30" s="25" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="L30" s="25" t="n">
-        <v>163</v>
+        <v>1302</v>
       </c>
       <c r="M30" s="26" t="n">
         <v>1.4</v>
       </c>
       <c r="N30" s="26" t="n">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="O30" s="27" t="n">
         <v>64.09999999999999</v>
       </c>
       <c r="P30" s="27" t="n">
-        <v>52326</v>
+        <v>52174</v>
       </c>
       <c r="Q30" s="28" t="inlineStr">
         <is>
@@ -2403,25 +2403,25 @@
         </is>
       </c>
       <c r="F31" s="22" t="n">
-        <v>169403</v>
+        <v>164755</v>
       </c>
       <c r="G31" s="23" t="n">
-        <v>34.8</v>
+        <v>35.3</v>
       </c>
       <c r="H31" s="23" t="n">
-        <v>58991</v>
+        <v>58159</v>
       </c>
       <c r="I31" s="24" t="n">
-        <v>64</v>
+        <v>59.7</v>
       </c>
       <c r="J31" s="24" t="n">
-        <v>108475</v>
+        <v>98359</v>
       </c>
       <c r="K31" s="25" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="L31" s="25" t="n">
-        <v>1444</v>
+        <v>7743</v>
       </c>
       <c r="M31" s="26" t="n">
         <v>0.3</v>
@@ -2430,10 +2430,10 @@
         <v>494</v>
       </c>
       <c r="O31" s="27" t="n">
-        <v>65.2</v>
+        <v>64.7</v>
       </c>
       <c r="P31" s="27" t="n">
-        <v>110413</v>
+        <v>106596</v>
       </c>
       <c r="Q31" s="28" t="inlineStr">
         <is>
@@ -2452,37 +2452,37 @@
         </is>
       </c>
       <c r="F32" s="22" t="n">
-        <v>41827</v>
+        <v>41210</v>
       </c>
       <c r="G32" s="23" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H32" s="23" t="n">
-        <v>1873</v>
+        <v>1731</v>
       </c>
       <c r="I32" s="24" t="n">
-        <v>83.2</v>
+        <v>78.2</v>
       </c>
       <c r="J32" s="24" t="n">
-        <v>34787</v>
+        <v>32226</v>
       </c>
       <c r="K32" s="25" t="n">
-        <v>10.5</v>
+        <v>15.7</v>
       </c>
       <c r="L32" s="25" t="n">
-        <v>4376</v>
+        <v>6470</v>
       </c>
       <c r="M32" s="26" t="n">
         <v>1.9</v>
       </c>
       <c r="N32" s="26" t="n">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="O32" s="27" t="n">
-        <v>95.5</v>
+        <v>95.8</v>
       </c>
       <c r="P32" s="27" t="n">
-        <v>39954</v>
+        <v>39479</v>
       </c>
       <c r="Q32" s="28" t="inlineStr">
         <is>
@@ -2501,37 +2501,37 @@
         </is>
       </c>
       <c r="F33" s="22" t="n">
-        <v>27235</v>
+        <v>26515</v>
       </c>
       <c r="G33" s="23" t="n">
-        <v>45.2</v>
+        <v>46.4</v>
       </c>
       <c r="H33" s="23" t="n">
-        <v>12309</v>
+        <v>12303</v>
       </c>
       <c r="I33" s="24" t="n">
-        <v>52.8</v>
+        <v>47</v>
       </c>
       <c r="J33" s="24" t="n">
-        <v>14384</v>
+        <v>12462</v>
       </c>
       <c r="K33" s="25" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="L33" s="25" t="n">
-        <v>556</v>
+        <v>1750</v>
       </c>
       <c r="M33" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O33" s="27" t="n">
-        <v>54.9</v>
+        <v>53.6</v>
       </c>
       <c r="P33" s="27" t="n">
-        <v>14952</v>
+        <v>14212</v>
       </c>
       <c r="Q33" s="28" t="inlineStr">
         <is>
@@ -2559,16 +2559,16 @@
         <v>7202</v>
       </c>
       <c r="I34" s="24" t="n">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J34" s="24" t="n">
-        <v>124654</v>
+        <v>122715</v>
       </c>
       <c r="K34" s="25" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="L34" s="25" t="n">
-        <v>4571</v>
+        <v>6648</v>
       </c>
       <c r="M34" s="26" t="n">
         <v>1.5</v>
@@ -2577,10 +2577,10 @@
         <v>2078</v>
       </c>
       <c r="O34" s="27" t="n">
-        <v>94.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="P34" s="27" t="n">
-        <v>131303</v>
+        <v>131441</v>
       </c>
       <c r="Q34" s="28" t="inlineStr">
         <is>
@@ -2648,25 +2648,25 @@
         </is>
       </c>
       <c r="F36" s="22" t="n">
-        <v>154582</v>
+        <v>135605</v>
       </c>
       <c r="G36" s="23" t="n">
-        <v>83.3</v>
+        <v>91.8</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>128803</v>
+        <v>124482</v>
       </c>
       <c r="I36" s="24" t="n">
         <v>1</v>
       </c>
       <c r="J36" s="24" t="n">
-        <v>1480</v>
+        <v>1349</v>
       </c>
       <c r="K36" s="25" t="n">
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="L36" s="25" t="n">
-        <v>5323</v>
+        <v>9774</v>
       </c>
       <c r="M36" s="26" t="n">
         <v>0</v>
@@ -2675,10 +2675,10 @@
         <v>0</v>
       </c>
       <c r="O36" s="27" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P36" s="27" t="n">
-        <v>6802</v>
+        <v>11123</v>
       </c>
       <c r="Q36" s="28" t="inlineStr">
         <is>
@@ -2755,16 +2755,16 @@
         <v>186957</v>
       </c>
       <c r="I38" s="24" t="n">
-        <v>68.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="J38" s="24" t="n">
-        <v>408446</v>
+        <v>406065</v>
       </c>
       <c r="K38" s="25" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L38" s="25" t="n">
-        <v>0</v>
+        <v>1786</v>
       </c>
       <c r="M38" s="26" t="n">
         <v>0</v>
@@ -2773,10 +2773,10 @@
         <v>0</v>
       </c>
       <c r="O38" s="27" t="n">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="P38" s="27" t="n">
-        <v>408446</v>
+        <v>407851</v>
       </c>
       <c r="Q38" s="28" t="inlineStr">
         <is>
@@ -2804,16 +2804,16 @@
         <v>147864</v>
       </c>
       <c r="I39" s="24" t="n">
-        <v>60.5</v>
+        <v>59.5</v>
       </c>
       <c r="J39" s="24" t="n">
-        <v>249881</v>
+        <v>245751</v>
       </c>
       <c r="K39" s="25" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="L39" s="25" t="n">
-        <v>12391</v>
+        <v>16934</v>
       </c>
       <c r="M39" s="26" t="n">
         <v>0.7</v>
@@ -2822,10 +2822,10 @@
         <v>2891</v>
       </c>
       <c r="O39" s="27" t="n">
-        <v>64.2</v>
+        <v>64.3</v>
       </c>
       <c r="P39" s="27" t="n">
-        <v>265163</v>
+        <v>265576</v>
       </c>
       <c r="Q39" s="28" t="inlineStr">
         <is>
@@ -2844,37 +2844,37 @@
         </is>
       </c>
       <c r="F40" s="22" t="n">
-        <v>182340</v>
+        <v>146977</v>
       </c>
       <c r="G40" s="23" t="n">
-        <v>49.3</v>
+        <v>61.1</v>
       </c>
       <c r="H40" s="23" t="n">
         <v>89803</v>
       </c>
       <c r="I40" s="24" t="n">
-        <v>50.3</v>
+        <v>38</v>
       </c>
       <c r="J40" s="24" t="n">
-        <v>91655</v>
+        <v>55851</v>
       </c>
       <c r="K40" s="25" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="L40" s="25" t="n">
-        <v>441</v>
+        <v>882</v>
       </c>
       <c r="M40" s="26" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N40" s="26" t="n">
         <v>441</v>
       </c>
       <c r="O40" s="27" t="n">
-        <v>50.7</v>
+        <v>38.9</v>
       </c>
       <c r="P40" s="27" t="n">
-        <v>92537</v>
+        <v>57174</v>
       </c>
       <c r="Q40" s="28" t="inlineStr">
         <is>
@@ -2893,25 +2893,25 @@
         </is>
       </c>
       <c r="F41" s="22" t="n">
-        <v>181819</v>
+        <v>180905</v>
       </c>
       <c r="G41" s="23" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="H41" s="23" t="n">
-        <v>27329</v>
+        <v>27317</v>
       </c>
       <c r="I41" s="24" t="n">
-        <v>82.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="J41" s="24" t="n">
-        <v>150141</v>
+        <v>148523</v>
       </c>
       <c r="K41" s="25" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L41" s="25" t="n">
-        <v>911</v>
+        <v>1628</v>
       </c>
       <c r="M41" s="26" t="n">
         <v>1.9</v>
@@ -2920,10 +2920,10 @@
         <v>3437</v>
       </c>
       <c r="O41" s="27" t="n">
-        <v>85</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="P41" s="27" t="n">
-        <v>154489</v>
+        <v>153588</v>
       </c>
       <c r="Q41" s="28" t="inlineStr">
         <is>
@@ -2942,19 +2942,19 @@
         </is>
       </c>
       <c r="F42" s="22" t="n">
-        <v>34646</v>
+        <v>33128</v>
       </c>
       <c r="G42" s="23" t="n">
-        <v>70.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H42" s="23" t="n">
-        <v>24362</v>
+        <v>24964</v>
       </c>
       <c r="I42" s="24" t="n">
-        <v>25.3</v>
+        <v>24.6</v>
       </c>
       <c r="J42" s="24" t="n">
-        <v>8766</v>
+        <v>8164</v>
       </c>
       <c r="K42" s="25" t="n">
         <v>0</v>
@@ -2969,10 +2969,10 @@
         <v>0</v>
       </c>
       <c r="O42" s="27" t="n">
-        <v>25.3</v>
+        <v>24.6</v>
       </c>
       <c r="P42" s="27" t="n">
-        <v>8766</v>
+        <v>8164</v>
       </c>
       <c r="Q42" s="28" t="inlineStr">
         <is>
@@ -2994,34 +2994,34 @@
         <v>71264</v>
       </c>
       <c r="G43" s="23" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="H43" s="23" t="n">
-        <v>12135</v>
+        <v>12390</v>
       </c>
       <c r="I43" s="24" t="n">
-        <v>76.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="J43" s="24" t="n">
-        <v>54265</v>
+        <v>53449</v>
       </c>
       <c r="K43" s="25" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="L43" s="25" t="n">
-        <v>947</v>
+        <v>1426</v>
       </c>
       <c r="M43" s="26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="N43" s="26" t="n">
-        <v>3916</v>
+        <v>3998</v>
       </c>
       <c r="O43" s="27" t="n">
-        <v>83</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="P43" s="27" t="n">
-        <v>59129</v>
+        <v>58874</v>
       </c>
       <c r="Q43" s="28" t="inlineStr">
         <is>
@@ -3040,37 +3040,37 @@
         </is>
       </c>
       <c r="F44" s="22" t="n">
-        <v>104103</v>
+        <v>104090</v>
       </c>
       <c r="G44" s="23" t="n">
-        <v>46.3</v>
+        <v>45.7</v>
       </c>
       <c r="H44" s="23" t="n">
-        <v>48187</v>
+        <v>47530</v>
       </c>
       <c r="I44" s="24" t="n">
-        <v>48.1</v>
+        <v>45.8</v>
       </c>
       <c r="J44" s="24" t="n">
-        <v>50044</v>
+        <v>47632</v>
       </c>
       <c r="K44" s="25" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="L44" s="25" t="n">
-        <v>2519</v>
+        <v>5621</v>
       </c>
       <c r="M44" s="26" t="n">
         <v>3.2</v>
       </c>
       <c r="N44" s="26" t="n">
-        <v>3352</v>
+        <v>3307</v>
       </c>
       <c r="O44" s="27" t="n">
-        <v>53.7</v>
+        <v>54.3</v>
       </c>
       <c r="P44" s="27" t="n">
-        <v>55916</v>
+        <v>56560</v>
       </c>
       <c r="Q44" s="28" t="inlineStr">
         <is>
@@ -3089,37 +3089,37 @@
         </is>
       </c>
       <c r="F45" s="22" t="n">
-        <v>773063</v>
+        <v>429795</v>
       </c>
       <c r="G45" s="23" t="n">
-        <v>31.6</v>
+        <v>37.1</v>
       </c>
       <c r="H45" s="23" t="n">
-        <v>244241</v>
+        <v>159454</v>
       </c>
       <c r="I45" s="24" t="n">
-        <v>64.90000000000001</v>
+        <v>52.9</v>
       </c>
       <c r="J45" s="24" t="n">
-        <v>501416</v>
+        <v>227362</v>
       </c>
       <c r="K45" s="25" t="n">
-        <v>2.8</v>
+        <v>8.6</v>
       </c>
       <c r="L45" s="25" t="n">
-        <v>21389</v>
+        <v>36962</v>
       </c>
       <c r="M45" s="26" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="N45" s="26" t="n">
         <v>6017</v>
       </c>
       <c r="O45" s="27" t="n">
-        <v>68.40000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="P45" s="27" t="n">
-        <v>528822</v>
+        <v>270341</v>
       </c>
       <c r="Q45" s="28" t="inlineStr">
         <is>
@@ -3138,37 +3138,37 @@
         </is>
       </c>
       <c r="F46" s="22" t="n">
-        <v>96838</v>
+        <v>95190</v>
       </c>
       <c r="G46" s="23" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="H46" s="23" t="n">
-        <v>26187</v>
+        <v>26177</v>
       </c>
       <c r="I46" s="24" t="n">
-        <v>65.2</v>
+        <v>60.3</v>
       </c>
       <c r="J46" s="24" t="n">
-        <v>63123</v>
+        <v>57400</v>
       </c>
       <c r="K46" s="25" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="L46" s="25" t="n">
-        <v>1618</v>
+        <v>5616</v>
       </c>
       <c r="M46" s="26" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="N46" s="26" t="n">
-        <v>5912</v>
+        <v>5902</v>
       </c>
       <c r="O46" s="27" t="n">
-        <v>73</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="P46" s="27" t="n">
-        <v>70653</v>
+        <v>68918</v>
       </c>
       <c r="Q46" s="28" t="inlineStr">
         <is>
@@ -3187,37 +3187,37 @@
         </is>
       </c>
       <c r="F47" s="22" t="n">
-        <v>111452</v>
+        <v>88050</v>
       </c>
       <c r="G47" s="23" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="H47" s="23" t="n">
-        <v>5667</v>
+        <v>4755</v>
       </c>
       <c r="I47" s="24" t="n">
-        <v>89.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="J47" s="24" t="n">
-        <v>100212</v>
+        <v>73874</v>
       </c>
       <c r="K47" s="25" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="L47" s="25" t="n">
-        <v>1224</v>
+        <v>5195</v>
       </c>
       <c r="M47" s="26" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="N47" s="26" t="n">
-        <v>4414</v>
+        <v>4226</v>
       </c>
       <c r="O47" s="27" t="n">
-        <v>95</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="P47" s="27" t="n">
-        <v>105850</v>
+        <v>83295</v>
       </c>
       <c r="Q47" s="28" t="inlineStr">
         <is>
@@ -3236,37 +3236,37 @@
         </is>
       </c>
       <c r="F48" s="22" t="n">
-        <v>78317</v>
+        <v>75185</v>
       </c>
       <c r="G48" s="23" t="n">
-        <v>53.9</v>
+        <v>55.5</v>
       </c>
       <c r="H48" s="23" t="n">
-        <v>42245</v>
+        <v>41728</v>
       </c>
       <c r="I48" s="24" t="n">
-        <v>41.6</v>
+        <v>36.5</v>
       </c>
       <c r="J48" s="24" t="n">
-        <v>32570</v>
+        <v>27443</v>
       </c>
       <c r="K48" s="25" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="L48" s="25" t="n">
-        <v>1071</v>
+        <v>3910</v>
       </c>
       <c r="M48" s="26" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N48" s="26" t="n">
-        <v>2428</v>
+        <v>2180</v>
       </c>
       <c r="O48" s="27" t="n">
-        <v>46.1</v>
+        <v>44.6</v>
       </c>
       <c r="P48" s="27" t="n">
-        <v>36070</v>
+        <v>33533</v>
       </c>
       <c r="Q48" s="28" t="inlineStr">
         <is>
@@ -3288,16 +3288,16 @@
         <v>54435</v>
       </c>
       <c r="G49" s="23" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="H49" s="23" t="n">
-        <v>26690</v>
+        <v>26874</v>
       </c>
       <c r="I49" s="24" t="n">
-        <v>44</v>
+        <v>43.6</v>
       </c>
       <c r="J49" s="24" t="n">
-        <v>23935</v>
+        <v>23725</v>
       </c>
       <c r="K49" s="25" t="n">
         <v>0</v>
@@ -3309,13 +3309,13 @@
         <v>7</v>
       </c>
       <c r="N49" s="26" t="n">
-        <v>3810</v>
+        <v>3836</v>
       </c>
       <c r="O49" s="27" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="P49" s="27" t="n">
-        <v>27745</v>
+        <v>27561</v>
       </c>
       <c r="Q49" s="28" t="inlineStr">
         <is>
@@ -3383,37 +3383,37 @@
         </is>
       </c>
       <c r="F51" s="22" t="n">
-        <v>216648</v>
+        <v>46005</v>
       </c>
       <c r="G51" s="23" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="H51" s="23" t="n">
-        <v>3056</v>
+        <v>1932</v>
       </c>
       <c r="I51" s="24" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="J51" s="24" t="n">
+        <v>37826</v>
+      </c>
+      <c r="K51" s="25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L51" s="25" t="n">
+        <v>5753</v>
+      </c>
+      <c r="M51" s="26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N51" s="26" t="n">
+        <v>494</v>
+      </c>
+      <c r="O51" s="27" t="n">
         <v>95.8</v>
       </c>
-      <c r="J51" s="24" t="n">
-        <v>207638</v>
-      </c>
-      <c r="K51" s="25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L51" s="25" t="n">
-        <v>5476</v>
-      </c>
-      <c r="M51" s="26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N51" s="26" t="n">
-        <v>478</v>
-      </c>
-      <c r="O51" s="27" t="n">
-        <v>98.59999999999999</v>
-      </c>
       <c r="P51" s="27" t="n">
-        <v>213592</v>
+        <v>44073</v>
       </c>
       <c r="Q51" s="28" t="inlineStr">
         <is>
@@ -3432,37 +3432,37 @@
         </is>
       </c>
       <c r="F52" s="22" t="n">
-        <v>92192</v>
+        <v>91440</v>
       </c>
       <c r="G52" s="23" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="H52" s="23" t="n">
-        <v>38963</v>
+        <v>38771</v>
       </c>
       <c r="I52" s="24" t="n">
-        <v>54.2</v>
+        <v>52.2</v>
       </c>
       <c r="J52" s="24" t="n">
-        <v>49968</v>
+        <v>47732</v>
       </c>
       <c r="K52" s="25" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="L52" s="25" t="n">
-        <v>1424</v>
+        <v>3109</v>
       </c>
       <c r="M52" s="26" t="n">
         <v>2</v>
       </c>
       <c r="N52" s="26" t="n">
-        <v>1838</v>
+        <v>1829</v>
       </c>
       <c r="O52" s="27" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="P52" s="27" t="n">
-        <v>53229</v>
+        <v>52669</v>
       </c>
       <c r="Q52" s="28" t="inlineStr">
         <is>
@@ -3481,37 +3481,37 @@
         </is>
       </c>
       <c r="F53" s="22" t="n">
-        <v>50683</v>
+        <v>45690</v>
       </c>
       <c r="G53" s="23" t="n">
-        <v>16.4</v>
+        <v>17.9</v>
       </c>
       <c r="H53" s="23" t="n">
-        <v>8333</v>
+        <v>8179</v>
       </c>
       <c r="I53" s="24" t="n">
-        <v>73.2</v>
+        <v>63.7</v>
       </c>
       <c r="J53" s="24" t="n">
-        <v>37122</v>
+        <v>29105</v>
       </c>
       <c r="K53" s="25" t="n">
-        <v>2.3</v>
+        <v>9.9</v>
       </c>
       <c r="L53" s="25" t="n">
-        <v>1146</v>
+        <v>4523</v>
       </c>
       <c r="M53" s="26" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="N53" s="26" t="n">
-        <v>4083</v>
+        <v>3838</v>
       </c>
       <c r="O53" s="27" t="n">
-        <v>83.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="P53" s="27" t="n">
-        <v>42350</v>
+        <v>37466</v>
       </c>
       <c r="Q53" s="28" t="inlineStr">
         <is>
@@ -3530,41 +3530,41 @@
         </is>
       </c>
       <c r="F54" s="22" t="n">
-        <v>36698</v>
+        <v>24060</v>
       </c>
       <c r="G54" s="23" t="n">
-        <v>6.6</v>
+        <v>9.5</v>
       </c>
       <c r="H54" s="23" t="n">
-        <v>2425</v>
+        <v>2286</v>
       </c>
       <c r="I54" s="24" t="n">
-        <v>83.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="J54" s="24" t="n">
-        <v>30790</v>
+        <v>16866</v>
       </c>
       <c r="K54" s="25" t="n">
-        <v>8.5</v>
+        <v>18.9</v>
       </c>
       <c r="L54" s="25" t="n">
-        <v>3122</v>
+        <v>4547</v>
       </c>
       <c r="M54" s="26" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N54" s="26" t="n">
         <v>361</v>
       </c>
       <c r="O54" s="27" t="n">
-        <v>93.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="P54" s="27" t="n">
-        <v>34274</v>
+        <v>21774</v>
       </c>
       <c r="Q54" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3579,41 +3579,41 @@
         </is>
       </c>
       <c r="F55" s="22" t="n">
-        <v>101240</v>
+        <v>98640</v>
       </c>
       <c r="G55" s="23" t="n">
-        <v>45.4</v>
+        <v>45.6</v>
       </c>
       <c r="H55" s="23" t="n">
-        <v>45924</v>
+        <v>44980</v>
       </c>
       <c r="I55" s="24" t="n">
-        <v>36.3</v>
+        <v>31.8</v>
       </c>
       <c r="J55" s="24" t="n">
-        <v>36714</v>
+        <v>31368</v>
       </c>
       <c r="K55" s="25" t="n">
-        <v>15.8</v>
+        <v>20</v>
       </c>
       <c r="L55" s="25" t="n">
-        <v>16009</v>
+        <v>19728</v>
       </c>
       <c r="M55" s="26" t="n">
         <v>2.6</v>
       </c>
       <c r="N55" s="26" t="n">
-        <v>2593</v>
+        <v>2565</v>
       </c>
       <c r="O55" s="27" t="n">
-        <v>54.6</v>
+        <v>54.4</v>
       </c>
       <c r="P55" s="27" t="n">
-        <v>55316</v>
+        <v>53660</v>
       </c>
       <c r="Q55" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3628,25 +3628,25 @@
         </is>
       </c>
       <c r="F56" s="22" t="n">
-        <v>61610</v>
+        <v>58000</v>
       </c>
       <c r="G56" s="23" t="n">
-        <v>40.7</v>
+        <v>42.5</v>
       </c>
       <c r="H56" s="23" t="n">
-        <v>25072</v>
+        <v>24650</v>
       </c>
       <c r="I56" s="24" t="n">
-        <v>57.2</v>
+        <v>45.2</v>
       </c>
       <c r="J56" s="24" t="n">
-        <v>35226</v>
+        <v>26216</v>
       </c>
       <c r="K56" s="25" t="n">
-        <v>1.9</v>
+        <v>12</v>
       </c>
       <c r="L56" s="25" t="n">
-        <v>1142</v>
+        <v>6960</v>
       </c>
       <c r="M56" s="26" t="n">
         <v>0.3</v>
@@ -3655,10 +3655,10 @@
         <v>174</v>
       </c>
       <c r="O56" s="27" t="n">
-        <v>59.3</v>
+        <v>57.5</v>
       </c>
       <c r="P56" s="27" t="n">
-        <v>36541</v>
+        <v>33350</v>
       </c>
       <c r="Q56" s="28" t="inlineStr">
         <is>
@@ -3680,34 +3680,34 @@
         <v>108035</v>
       </c>
       <c r="G57" s="23" t="n">
-        <v>26.2</v>
+        <v>23.9</v>
       </c>
       <c r="H57" s="23" t="n">
-        <v>28261</v>
+        <v>25802</v>
       </c>
       <c r="I57" s="24" t="n">
-        <v>34.6</v>
+        <v>30.5</v>
       </c>
       <c r="J57" s="24" t="n">
-        <v>37381</v>
+        <v>32923</v>
       </c>
       <c r="K57" s="25" t="n">
-        <v>22.6</v>
+        <v>30.5</v>
       </c>
       <c r="L57" s="25" t="n">
-        <v>24457</v>
+        <v>32934</v>
       </c>
       <c r="M57" s="26" t="n">
-        <v>16.6</v>
+        <v>15.2</v>
       </c>
       <c r="N57" s="26" t="n">
-        <v>17936</v>
+        <v>16376</v>
       </c>
       <c r="O57" s="27" t="n">
-        <v>73.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="P57" s="27" t="n">
-        <v>79774</v>
+        <v>82233</v>
       </c>
       <c r="Q57" s="28" t="inlineStr">
         <is>
@@ -3726,37 +3726,37 @@
         </is>
       </c>
       <c r="F58" s="22" t="n">
-        <v>142667</v>
+        <v>140414</v>
       </c>
       <c r="G58" s="23" t="n">
-        <v>93.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H58" s="23" t="n">
-        <v>133562</v>
+        <v>133216</v>
       </c>
       <c r="I58" s="24" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J58" s="24" t="n">
-        <v>2842</v>
+        <v>2497</v>
       </c>
       <c r="K58" s="25" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="L58" s="25" t="n">
-        <v>2568</v>
+        <v>3263</v>
       </c>
       <c r="M58" s="26" t="n">
         <v>1</v>
       </c>
       <c r="N58" s="26" t="n">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="O58" s="27" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="P58" s="27" t="n">
-        <v>6852</v>
+        <v>7198</v>
       </c>
       <c r="Q58" s="28" t="inlineStr">
         <is>
@@ -3778,34 +3778,34 @@
         <v>22213</v>
       </c>
       <c r="G59" s="23" t="n">
-        <v>31.1</v>
+        <v>31.3</v>
       </c>
       <c r="H59" s="23" t="n">
-        <v>6917</v>
+        <v>6953</v>
       </c>
       <c r="I59" s="24" t="n">
-        <v>60.2</v>
+        <v>58.4</v>
       </c>
       <c r="J59" s="24" t="n">
-        <v>13374</v>
+        <v>12970</v>
       </c>
       <c r="K59" s="25" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="L59" s="25" t="n">
-        <v>747</v>
+        <v>1107</v>
       </c>
       <c r="M59" s="26" t="n">
         <v>5.3</v>
       </c>
       <c r="N59" s="26" t="n">
-        <v>1176</v>
+        <v>1182</v>
       </c>
       <c r="O59" s="27" t="n">
-        <v>68.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="P59" s="27" t="n">
-        <v>15296</v>
+        <v>15260</v>
       </c>
       <c r="Q59" s="28" t="inlineStr">
         <is>
@@ -3830,31 +3830,31 @@
         <v>3.2</v>
       </c>
       <c r="H60" s="30" t="n">
-        <v>3847</v>
+        <v>3832</v>
       </c>
       <c r="I60" s="31" t="n">
-        <v>90.3</v>
+        <v>89.5</v>
       </c>
       <c r="J60" s="31" t="n">
-        <v>108217</v>
+        <v>107273</v>
       </c>
       <c r="K60" s="32" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="L60" s="32" t="n">
-        <v>1242</v>
+        <v>2227</v>
       </c>
       <c r="M60" s="33" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="N60" s="33" t="n">
-        <v>6544</v>
+        <v>6518</v>
       </c>
       <c r="O60" s="34" t="n">
         <v>96.8</v>
       </c>
       <c r="P60" s="34" t="n">
-        <v>116003</v>
+        <v>116018</v>
       </c>
       <c r="Q60" s="28" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
       <c r="D6" s="21" t="n"/>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>SO1603</t>
+          <t>SO1702</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -3997,25 +3997,25 @@
         </is>
       </c>
       <c r="G6" s="22" t="n">
-        <v>43330</v>
+        <v>60130</v>
       </c>
       <c r="H6" s="23" t="n">
-        <v>92</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>39871</v>
+        <v>58095</v>
       </c>
       <c r="J6" s="24" t="n">
-        <v>7.8</v>
+        <v>3.4</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>3398</v>
+        <v>2035</v>
       </c>
       <c r="L6" s="25" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="25" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N6" s="26" t="n">
         <v>0</v>
@@ -4024,10 +4024,10 @@
         <v>0</v>
       </c>
       <c r="P6" s="27" t="n">
-        <v>8</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" s="27" t="n">
-        <v>3459</v>
+        <v>2035</v>
       </c>
       <c r="R6" s="28" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
       <c r="D7" s="21" t="n"/>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>SO1606</t>
+          <t>SO1804</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -4051,41 +4051,41 @@
         </is>
       </c>
       <c r="G7" s="22" t="n">
-        <v>76115</v>
+        <v>107255</v>
       </c>
       <c r="H7" s="23" t="n">
-        <v>40.1</v>
+        <v>21.2</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>30545</v>
+        <v>22739</v>
       </c>
       <c r="J7" s="24" t="n">
-        <v>58.9</v>
+        <v>42.2</v>
       </c>
       <c r="K7" s="24" t="n">
-        <v>44842</v>
+        <v>45241</v>
       </c>
       <c r="L7" s="25" t="n">
-        <v>0.5</v>
+        <v>36.6</v>
       </c>
       <c r="M7" s="25" t="n">
-        <v>350</v>
+        <v>39275</v>
       </c>
       <c r="N7" s="26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O7" s="26" t="n">
-        <v>378</v>
+        <v>0</v>
       </c>
       <c r="P7" s="27" t="n">
-        <v>59.9</v>
+        <v>78.8</v>
       </c>
       <c r="Q7" s="27" t="n">
-        <v>45570</v>
+        <v>84516</v>
       </c>
       <c r="R7" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       <c r="D8" s="21" t="n"/>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>SO1702</t>
+          <t>SO2102</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -4105,19 +4105,19 @@
         </is>
       </c>
       <c r="G8" s="22" t="n">
-        <v>60130</v>
+        <v>28365</v>
       </c>
       <c r="H8" s="23" t="n">
-        <v>96.3</v>
+        <v>0</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>57899</v>
+        <v>0</v>
       </c>
       <c r="J8" s="24" t="n">
-        <v>3.7</v>
+        <v>100</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>2231</v>
+        <v>28365</v>
       </c>
       <c r="L8" s="25" t="n">
         <v>0</v>
@@ -4132,14 +4132,14 @@
         <v>0</v>
       </c>
       <c r="P8" s="27" t="n">
-        <v>3.7</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="27" t="n">
-        <v>2231</v>
+        <v>28365</v>
       </c>
       <c r="R8" s="28" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       <c r="D9" s="21" t="n"/>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>SO1804</t>
+          <t>SO2103</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -4159,25 +4159,25 @@
         </is>
       </c>
       <c r="G9" s="22" t="n">
-        <v>107255</v>
+        <v>135605</v>
       </c>
       <c r="H9" s="23" t="n">
-        <v>27</v>
+        <v>91.8</v>
       </c>
       <c r="I9" s="23" t="n">
-        <v>29000</v>
+        <v>124482</v>
       </c>
       <c r="J9" s="24" t="n">
-        <v>56.1</v>
+        <v>1</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>60166</v>
+        <v>1349</v>
       </c>
       <c r="L9" s="25" t="n">
-        <v>16.9</v>
+        <v>7.2</v>
       </c>
       <c r="M9" s="25" t="n">
-        <v>18088</v>
+        <v>9774</v>
       </c>
       <c r="N9" s="26" t="n">
         <v>0</v>
@@ -4186,14 +4186,14 @@
         <v>0</v>
       </c>
       <c r="P9" s="27" t="n">
-        <v>73</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q9" s="27" t="n">
-        <v>78255</v>
+        <v>11123</v>
       </c>
       <c r="R9" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       <c r="D10" s="21" t="n"/>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>SO2102</t>
+          <t>SO2104</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -4213,25 +4213,25 @@
         </is>
       </c>
       <c r="G10" s="22" t="n">
-        <v>28365</v>
+        <v>23345</v>
       </c>
       <c r="H10" s="23" t="n">
-        <v>0</v>
+        <v>16.9</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>0</v>
+        <v>3956</v>
       </c>
       <c r="J10" s="24" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>28365</v>
+        <v>19132</v>
       </c>
       <c r="L10" s="25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M10" s="25" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="N10" s="26" t="n">
         <v>0</v>
@@ -4240,10 +4240,10 @@
         <v>0</v>
       </c>
       <c r="P10" s="27" t="n">
-        <v>100</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="Q10" s="27" t="n">
-        <v>28365</v>
+        <v>19389</v>
       </c>
       <c r="R10" s="28" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
       <c r="D11" s="21" t="n"/>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>SO2103</t>
+          <t>SO2303</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -4267,25 +4267,25 @@
         </is>
       </c>
       <c r="G11" s="22" t="n">
-        <v>135605</v>
+        <v>33128</v>
       </c>
       <c r="H11" s="23" t="n">
-        <v>95</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I11" s="23" t="n">
-        <v>128803</v>
+        <v>24964</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>1.1</v>
+        <v>24.6</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>1480</v>
+        <v>8164</v>
       </c>
       <c r="L11" s="25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="M11" s="25" t="n">
-        <v>5323</v>
+        <v>0</v>
       </c>
       <c r="N11" s="26" t="n">
         <v>0</v>
@@ -4294,14 +4294,14 @@
         <v>0</v>
       </c>
       <c r="P11" s="27" t="n">
-        <v>5</v>
+        <v>24.6</v>
       </c>
       <c r="Q11" s="27" t="n">
-        <v>6802</v>
+        <v>8164</v>
       </c>
       <c r="R11" s="28" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4312,7 @@
       <c r="D12" s="21" t="n"/>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>SO2104</t>
+          <t>SO2305</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -4321,37 +4321,37 @@
         </is>
       </c>
       <c r="G12" s="22" t="n">
-        <v>23345</v>
+        <v>71264</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>16.9</v>
+        <v>17.4</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>3956</v>
+        <v>12390</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>19132</v>
+        <v>53449</v>
       </c>
       <c r="L12" s="25" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="25" t="n">
-        <v>257</v>
+        <v>1426</v>
       </c>
       <c r="N12" s="26" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O12" s="26" t="n">
-        <v>0</v>
+        <v>3998</v>
       </c>
       <c r="P12" s="27" t="n">
-        <v>83.09999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="Q12" s="27" t="n">
-        <v>19389</v>
+        <v>58874</v>
       </c>
       <c r="R12" s="28" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>SO2303</t>
+          <t>SO2307</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -4375,37 +4375,37 @@
         </is>
       </c>
       <c r="G13" s="22" t="n">
-        <v>33128</v>
+        <v>104090</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>73.5</v>
+        <v>45.7</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>24362</v>
+        <v>47530</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>26.5</v>
+        <v>45.8</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>8766</v>
+        <v>47632</v>
       </c>
       <c r="L13" s="25" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M13" s="25" t="n">
-        <v>0</v>
+        <v>5621</v>
       </c>
       <c r="N13" s="26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O13" s="26" t="n">
-        <v>0</v>
+        <v>3307</v>
       </c>
       <c r="P13" s="27" t="n">
-        <v>26.5</v>
+        <v>54.3</v>
       </c>
       <c r="Q13" s="27" t="n">
-        <v>8766</v>
+        <v>56560</v>
       </c>
       <c r="R13" s="28" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>SO2305</t>
+          <t>SO2501</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -4429,37 +4429,37 @@
         </is>
       </c>
       <c r="G14" s="22" t="n">
-        <v>71264</v>
+        <v>54435</v>
       </c>
       <c r="H14" s="23" t="n">
-        <v>17</v>
+        <v>49.4</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>12135</v>
+        <v>26874</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>76.09999999999999</v>
+        <v>43.6</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>54265</v>
+        <v>23725</v>
       </c>
       <c r="L14" s="25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M14" s="25" t="n">
-        <v>947</v>
+        <v>0</v>
       </c>
       <c r="N14" s="26" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="O14" s="26" t="n">
-        <v>3916</v>
+        <v>3836</v>
       </c>
       <c r="P14" s="27" t="n">
-        <v>83</v>
+        <v>50.6</v>
       </c>
       <c r="Q14" s="27" t="n">
-        <v>59129</v>
+        <v>27561</v>
       </c>
       <c r="R14" s="28" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
       <c r="D15" s="21" t="n"/>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>SO2307</t>
+          <t>SO2601</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -4483,37 +4483,37 @@
         </is>
       </c>
       <c r="G15" s="22" t="n">
-        <v>104090</v>
+        <v>46005</v>
       </c>
       <c r="H15" s="23" t="n">
-        <v>46.3</v>
+        <v>4.2</v>
       </c>
       <c r="I15" s="23" t="n">
-        <v>48182</v>
+        <v>1932</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>48.1</v>
+        <v>82.2</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>50042</v>
+        <v>37826</v>
       </c>
       <c r="L15" s="25" t="n">
-        <v>2.4</v>
+        <v>12.5</v>
       </c>
       <c r="M15" s="25" t="n">
-        <v>2514</v>
+        <v>5753</v>
       </c>
       <c r="N15" s="26" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="O15" s="26" t="n">
-        <v>3352</v>
+        <v>494</v>
       </c>
       <c r="P15" s="27" t="n">
-        <v>53.7</v>
+        <v>95.8</v>
       </c>
       <c r="Q15" s="27" t="n">
-        <v>55908</v>
+        <v>44073</v>
       </c>
       <c r="R15" s="28" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
       <c r="D16" s="21" t="n"/>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>SO2501</t>
+          <t>SO2801</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -4537,41 +4537,41 @@
         </is>
       </c>
       <c r="G16" s="22" t="n">
-        <v>54435</v>
+        <v>108035</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>49</v>
+        <v>23.9</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>26690</v>
+        <v>25802</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>44</v>
+        <v>30.5</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>23935</v>
+        <v>32923</v>
       </c>
       <c r="L16" s="25" t="n">
-        <v>0</v>
+        <v>30.5</v>
       </c>
       <c r="M16" s="25" t="n">
-        <v>0</v>
+        <v>32934</v>
       </c>
       <c r="N16" s="26" t="n">
-        <v>7</v>
+        <v>15.2</v>
       </c>
       <c r="O16" s="26" t="n">
-        <v>3810</v>
+        <v>16376</v>
       </c>
       <c r="P16" s="27" t="n">
-        <v>51</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="Q16" s="27" t="n">
-        <v>27745</v>
+        <v>82233</v>
       </c>
       <c r="R16" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       <c r="D17" s="21" t="n"/>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>SO2601</t>
+          <t>SO2802</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -4591,41 +4591,41 @@
         </is>
       </c>
       <c r="G17" s="22" t="n">
-        <v>46005</v>
+        <v>140414</v>
       </c>
       <c r="H17" s="23" t="n">
-        <v>4.1</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I17" s="23" t="n">
-        <v>1870</v>
+        <v>133216</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>87</v>
+        <v>1.8</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>40004</v>
+        <v>2497</v>
       </c>
       <c r="L17" s="25" t="n">
-        <v>7.9</v>
+        <v>2.3</v>
       </c>
       <c r="M17" s="25" t="n">
-        <v>3653</v>
+        <v>3263</v>
       </c>
       <c r="N17" s="26" t="n">
         <v>1</v>
       </c>
       <c r="O17" s="26" t="n">
-        <v>478</v>
+        <v>1438</v>
       </c>
       <c r="P17" s="27" t="n">
-        <v>95.90000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="Q17" s="27" t="n">
-        <v>44135</v>
+        <v>7198</v>
       </c>
       <c r="R17" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       <c r="D18" s="21" t="n"/>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>SO2801</t>
+          <t>SO2803</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -4645,41 +4645,41 @@
         </is>
       </c>
       <c r="G18" s="22" t="n">
-        <v>108035</v>
+        <v>22213</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>26.2</v>
+        <v>31.3</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>28261</v>
+        <v>6953</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>34.6</v>
+        <v>58.4</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>37381</v>
+        <v>12970</v>
       </c>
       <c r="L18" s="25" t="n">
-        <v>22.6</v>
+        <v>5</v>
       </c>
       <c r="M18" s="25" t="n">
-        <v>24457</v>
+        <v>1107</v>
       </c>
       <c r="N18" s="26" t="n">
-        <v>16.6</v>
+        <v>5.3</v>
       </c>
       <c r="O18" s="26" t="n">
-        <v>17936</v>
+        <v>1182</v>
       </c>
       <c r="P18" s="27" t="n">
-        <v>73.8</v>
+        <v>68.7</v>
       </c>
       <c r="Q18" s="27" t="n">
-        <v>79774</v>
+        <v>15260</v>
       </c>
       <c r="R18" s="28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
       <c r="D19" s="21" t="n"/>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>SO2802</t>
+          <t>SO2804</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -4699,41 +4699,41 @@
         </is>
       </c>
       <c r="G19" s="22" t="n">
-        <v>140414</v>
+        <v>119850</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>95.09999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>133562</v>
+        <v>3832</v>
       </c>
       <c r="J19" s="24" t="n">
-        <v>2</v>
+        <v>89.5</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>2842</v>
+        <v>107273</v>
       </c>
       <c r="L19" s="25" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="M19" s="25" t="n">
-        <v>2568</v>
+        <v>2227</v>
       </c>
       <c r="N19" s="26" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="O19" s="26" t="n">
-        <v>1442</v>
+        <v>6518</v>
       </c>
       <c r="P19" s="27" t="n">
-        <v>4.9</v>
+        <v>96.8</v>
       </c>
       <c r="Q19" s="27" t="n">
-        <v>6852</v>
+        <v>116018</v>
       </c>
       <c r="R19" s="28" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       <c r="D20" s="21" t="n"/>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>SO2803</t>
+          <t>SO1101</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -4753,37 +4753,37 @@
         </is>
       </c>
       <c r="G20" s="22" t="n">
-        <v>22213</v>
+        <v>301018</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>31.1</v>
+        <v>62.8</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>6917</v>
+        <v>189039</v>
       </c>
       <c r="J20" s="24" t="n">
-        <v>60.2</v>
+        <v>33.4</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>13374</v>
+        <v>100540</v>
       </c>
       <c r="L20" s="25" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="M20" s="25" t="n">
-        <v>747</v>
+        <v>11439</v>
       </c>
       <c r="N20" s="26" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O20" s="26" t="n">
-        <v>1176</v>
+        <v>0</v>
       </c>
       <c r="P20" s="27" t="n">
-        <v>68.90000000000001</v>
+        <v>37.2</v>
       </c>
       <c r="Q20" s="27" t="n">
-        <v>15296</v>
+        <v>111979</v>
       </c>
       <c r="R20" s="28" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
       <c r="D21" s="21" t="n"/>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>SO2804</t>
+          <t>SO1102</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -4807,37 +4807,37 @@
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>119850</v>
+        <v>26975</v>
       </c>
       <c r="H21" s="23" t="n">
-        <v>3.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>3847</v>
+        <v>17507</v>
       </c>
       <c r="J21" s="24" t="n">
-        <v>90.3</v>
+        <v>33.2</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>108217</v>
+        <v>8956</v>
       </c>
       <c r="L21" s="25" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="M21" s="25" t="n">
-        <v>1242</v>
+        <v>513</v>
       </c>
       <c r="N21" s="26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O21" s="26" t="n">
-        <v>6544</v>
+        <v>0</v>
       </c>
       <c r="P21" s="27" t="n">
-        <v>96.8</v>
+        <v>35.1</v>
       </c>
       <c r="Q21" s="27" t="n">
-        <v>116003</v>
+        <v>9468</v>
       </c>
       <c r="R21" s="28" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
       <c r="D22" s="21" t="n"/>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>SO1101</t>
+          <t>SO1201</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -4861,25 +4861,25 @@
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>301018</v>
+        <v>458640</v>
       </c>
       <c r="H22" s="23" t="n">
-        <v>62.8</v>
+        <v>38.7</v>
       </c>
       <c r="I22" s="23" t="n">
-        <v>189039</v>
+        <v>177494</v>
       </c>
       <c r="J22" s="24" t="n">
-        <v>33.4</v>
+        <v>55.2</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>100540</v>
+        <v>253169</v>
       </c>
       <c r="L22" s="25" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="M22" s="25" t="n">
-        <v>11439</v>
+        <v>27518</v>
       </c>
       <c r="N22" s="26" t="n">
         <v>0</v>
@@ -4888,10 +4888,10 @@
         <v>0</v>
       </c>
       <c r="P22" s="27" t="n">
-        <v>37.2</v>
+        <v>61.2</v>
       </c>
       <c r="Q22" s="27" t="n">
-        <v>111979</v>
+        <v>280688</v>
       </c>
       <c r="R22" s="28" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
       <c r="D23" s="21" t="n"/>
       <c r="E23" s="22" t="inlineStr">
         <is>
-          <t>SO1102</t>
+          <t>SO1401</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -4915,25 +4915,25 @@
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>26975</v>
+        <v>127135</v>
       </c>
       <c r="H23" s="23" t="n">
-        <v>64.90000000000001</v>
+        <v>22.2</v>
       </c>
       <c r="I23" s="23" t="n">
-        <v>17507</v>
+        <v>28224</v>
       </c>
       <c r="J23" s="24" t="n">
-        <v>33.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>8956</v>
+        <v>95478</v>
       </c>
       <c r="L23" s="25" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="M23" s="25" t="n">
-        <v>513</v>
+        <v>3433</v>
       </c>
       <c r="N23" s="26" t="n">
         <v>0</v>
@@ -4942,10 +4942,10 @@
         <v>0</v>
       </c>
       <c r="P23" s="27" t="n">
-        <v>35.1</v>
+        <v>77.8</v>
       </c>
       <c r="Q23" s="27" t="n">
-        <v>9468</v>
+        <v>98911</v>
       </c>
       <c r="R23" s="28" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
       <c r="D24" s="21" t="n"/>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>SO1201</t>
+          <t>SO1502</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -4969,37 +4969,37 @@
         </is>
       </c>
       <c r="G24" s="22" t="n">
-        <v>458640</v>
+        <v>47705</v>
       </c>
       <c r="H24" s="23" t="n">
-        <v>38.7</v>
+        <v>65.7</v>
       </c>
       <c r="I24" s="23" t="n">
-        <v>177494</v>
+        <v>31342</v>
       </c>
       <c r="J24" s="24" t="n">
-        <v>55.2</v>
+        <v>33.6</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>253169</v>
+        <v>16029</v>
       </c>
       <c r="L24" s="25" t="n">
-        <v>6</v>
+        <v>0.3</v>
       </c>
       <c r="M24" s="25" t="n">
-        <v>27518</v>
+        <v>143</v>
       </c>
       <c r="N24" s="26" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O24" s="26" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="P24" s="27" t="n">
-        <v>61.2</v>
+        <v>34.2</v>
       </c>
       <c r="Q24" s="27" t="n">
-        <v>280688</v>
+        <v>16315</v>
       </c>
       <c r="R24" s="28" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
       <c r="D25" s="21" t="n"/>
       <c r="E25" s="22" t="inlineStr">
         <is>
-          <t>SO1401</t>
+          <t>SO1601</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -5023,37 +5023,37 @@
         </is>
       </c>
       <c r="G25" s="22" t="n">
-        <v>127135</v>
+        <v>361685</v>
       </c>
       <c r="H25" s="23" t="n">
-        <v>22.2</v>
+        <v>42</v>
       </c>
       <c r="I25" s="23" t="n">
-        <v>28224</v>
+        <v>151908</v>
       </c>
       <c r="J25" s="24" t="n">
-        <v>75.09999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>95478</v>
+        <v>207607</v>
       </c>
       <c r="L25" s="25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M25" s="25" t="n">
-        <v>3433</v>
+        <v>0</v>
       </c>
       <c r="N25" s="26" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O25" s="26" t="n">
-        <v>0</v>
+        <v>2170</v>
       </c>
       <c r="P25" s="27" t="n">
-        <v>77.8</v>
+        <v>58</v>
       </c>
       <c r="Q25" s="27" t="n">
-        <v>98911</v>
+        <v>209777</v>
       </c>
       <c r="R25" s="28" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
       <c r="D26" s="21" t="n"/>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>SO1502</t>
+          <t>SO1602</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -5077,37 +5077,37 @@
         </is>
       </c>
       <c r="G26" s="22" t="n">
-        <v>47705</v>
+        <v>23305</v>
       </c>
       <c r="H26" s="23" t="n">
-        <v>65.7</v>
+        <v>52</v>
       </c>
       <c r="I26" s="23" t="n">
-        <v>31342</v>
+        <v>12119</v>
       </c>
       <c r="J26" s="24" t="n">
-        <v>33.6</v>
+        <v>47.5</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>16029</v>
+        <v>11070</v>
       </c>
       <c r="L26" s="25" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M26" s="25" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="N26" s="26" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="O26" s="26" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="P26" s="27" t="n">
-        <v>34.2</v>
+        <v>48</v>
       </c>
       <c r="Q26" s="27" t="n">
-        <v>16315</v>
+        <v>11186</v>
       </c>
       <c r="R26" s="28" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
       <c r="D27" s="21" t="n"/>
       <c r="E27" s="22" t="inlineStr">
         <is>
-          <t>SO1601</t>
+          <t>SO1603</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -5131,37 +5131,37 @@
         </is>
       </c>
       <c r="G27" s="22" t="n">
-        <v>361685</v>
+        <v>43330</v>
       </c>
       <c r="H27" s="23" t="n">
-        <v>42</v>
+        <v>56.1</v>
       </c>
       <c r="I27" s="23" t="n">
-        <v>151908</v>
+        <v>24308</v>
       </c>
       <c r="J27" s="24" t="n">
-        <v>57.4</v>
+        <v>40.9</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>207607</v>
+        <v>17722</v>
       </c>
       <c r="L27" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M27" s="25" t="n">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="N27" s="26" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O27" s="26" t="n">
-        <v>2170</v>
+        <v>0</v>
       </c>
       <c r="P27" s="27" t="n">
-        <v>58</v>
+        <v>43.9</v>
       </c>
       <c r="Q27" s="27" t="n">
-        <v>209777</v>
+        <v>19022</v>
       </c>
       <c r="R27" s="28" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
       <c r="D28" s="21" t="n"/>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>SO1602</t>
+          <t>SO1606</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -5185,37 +5185,37 @@
         </is>
       </c>
       <c r="G28" s="22" t="n">
-        <v>23305</v>
+        <v>76115</v>
       </c>
       <c r="H28" s="23" t="n">
-        <v>52</v>
+        <v>35.2</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>12119</v>
+        <v>26792</v>
       </c>
       <c r="J28" s="24" t="n">
-        <v>47.5</v>
+        <v>59.7</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>11070</v>
+        <v>45441</v>
       </c>
       <c r="L28" s="25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M28" s="25" t="n">
-        <v>0</v>
+        <v>2892</v>
       </c>
       <c r="N28" s="26" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="O28" s="26" t="n">
-        <v>117</v>
+        <v>989</v>
       </c>
       <c r="P28" s="27" t="n">
-        <v>48</v>
+        <v>64.8</v>
       </c>
       <c r="Q28" s="27" t="n">
-        <v>11186</v>
+        <v>49323</v>
       </c>
       <c r="R28" s="28" t="inlineStr">
         <is>
@@ -5248,16 +5248,16 @@
         <v>17003</v>
       </c>
       <c r="J29" s="24" t="n">
-        <v>53.8</v>
+        <v>51.9</v>
       </c>
       <c r="K29" s="24" t="n">
-        <v>22421</v>
+        <v>21629</v>
       </c>
       <c r="L29" s="25" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="M29" s="25" t="n">
-        <v>1667</v>
+        <v>2459</v>
       </c>
       <c r="N29" s="26" t="n">
         <v>1.4</v>
@@ -5302,16 +5302,16 @@
         <v>14315</v>
       </c>
       <c r="J30" s="24" t="n">
-        <v>59.1</v>
+        <v>53.5</v>
       </c>
       <c r="K30" s="24" t="n">
-        <v>22381</v>
+        <v>20260</v>
       </c>
       <c r="L30" s="25" t="n">
-        <v>3.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M30" s="25" t="n">
-        <v>1174</v>
+        <v>3295</v>
       </c>
       <c r="N30" s="26" t="n">
         <v>0</v>
@@ -5356,16 +5356,16 @@
         <v>72798</v>
       </c>
       <c r="J31" s="24" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="K31" s="24" t="n">
-        <v>13979</v>
+        <v>13188</v>
       </c>
       <c r="L31" s="25" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="M31" s="25" t="n">
-        <v>879</v>
+        <v>1670</v>
       </c>
       <c r="N31" s="26" t="n">
         <v>0.3</v>
@@ -5410,16 +5410,16 @@
         <v>24451</v>
       </c>
       <c r="J32" s="24" t="n">
-        <v>47.2</v>
+        <v>42.9</v>
       </c>
       <c r="K32" s="24" t="n">
-        <v>26902</v>
+        <v>24451</v>
       </c>
       <c r="L32" s="25" t="n">
-        <v>9.800000000000001</v>
+        <v>14.2</v>
       </c>
       <c r="M32" s="25" t="n">
-        <v>5586</v>
+        <v>8093</v>
       </c>
       <c r="N32" s="26" t="n">
         <v>0</v>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="P32" s="27" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
       <c r="Q32" s="27" t="n">
-        <v>32487</v>
+        <v>32544</v>
       </c>
       <c r="R32" s="28" t="inlineStr">
         <is>
@@ -5464,16 +5464,16 @@
         <v>38069</v>
       </c>
       <c r="J33" s="24" t="n">
-        <v>56.1</v>
+        <v>53.8</v>
       </c>
       <c r="K33" s="24" t="n">
-        <v>51093</v>
+        <v>48998</v>
       </c>
       <c r="L33" s="25" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="M33" s="25" t="n">
-        <v>1184</v>
+        <v>3279</v>
       </c>
       <c r="N33" s="26" t="n">
         <v>0.8</v>
@@ -5518,16 +5518,16 @@
         <v>20574</v>
       </c>
       <c r="J34" s="24" t="n">
-        <v>73.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="K34" s="24" t="n">
-        <v>59211</v>
+        <v>57105</v>
       </c>
       <c r="L34" s="25" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="M34" s="25" t="n">
-        <v>1296</v>
+        <v>3321</v>
       </c>
       <c r="N34" s="26" t="n">
         <v>0</v>
@@ -5536,10 +5536,10 @@
         <v>0</v>
       </c>
       <c r="P34" s="27" t="n">
-        <v>74.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q34" s="27" t="n">
-        <v>60507</v>
+        <v>60426</v>
       </c>
       <c r="R34" s="28" t="inlineStr">
         <is>
@@ -5572,16 +5572,16 @@
         <v>12388</v>
       </c>
       <c r="J35" s="24" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="K35" s="24" t="n">
-        <v>15767</v>
+        <v>13233</v>
       </c>
       <c r="L35" s="25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M35" s="25" t="n">
-        <v>0</v>
+        <v>2534</v>
       </c>
       <c r="N35" s="26" t="n">
         <v>0</v>
@@ -5626,16 +5626,16 @@
         <v>84637</v>
       </c>
       <c r="J36" s="24" t="n">
-        <v>45.3</v>
+        <v>44.8</v>
       </c>
       <c r="K36" s="24" t="n">
-        <v>71397</v>
+        <v>70609</v>
       </c>
       <c r="L36" s="25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M36" s="25" t="n">
-        <v>0</v>
+        <v>788</v>
       </c>
       <c r="N36" s="26" t="n">
         <v>1</v>
@@ -5680,16 +5680,16 @@
         <v>238260</v>
       </c>
       <c r="J37" s="24" t="n">
-        <v>41.1</v>
+        <v>38.6</v>
       </c>
       <c r="K37" s="24" t="n">
-        <v>193528</v>
+        <v>181756</v>
       </c>
       <c r="L37" s="25" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="M37" s="25" t="n">
-        <v>15539</v>
+        <v>27310</v>
       </c>
       <c r="N37" s="26" t="n">
         <v>5</v>
@@ -5734,16 +5734,16 @@
         <v>63667</v>
       </c>
       <c r="J38" s="24" t="n">
-        <v>28.4</v>
+        <v>26.4</v>
       </c>
       <c r="K38" s="24" t="n">
-        <v>25611</v>
+        <v>23808</v>
       </c>
       <c r="L38" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M38" s="25" t="n">
-        <v>902</v>
+        <v>2705</v>
       </c>
       <c r="N38" s="26" t="n">
         <v>0</v>
@@ -5842,16 +5842,16 @@
         <v>38611</v>
       </c>
       <c r="J40" s="24" t="n">
-        <v>60.1</v>
+        <v>59.8</v>
       </c>
       <c r="K40" s="24" t="n">
-        <v>92085</v>
+        <v>91626</v>
       </c>
       <c r="L40" s="25" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="M40" s="25" t="n">
-        <v>22523</v>
+        <v>22983</v>
       </c>
       <c r="N40" s="26" t="n">
         <v>0</v>
@@ -5896,16 +5896,16 @@
         <v>56387</v>
       </c>
       <c r="J41" s="24" t="n">
-        <v>52.5</v>
+        <v>51.4</v>
       </c>
       <c r="K41" s="24" t="n">
-        <v>64635</v>
+        <v>63281</v>
       </c>
       <c r="L41" s="25" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="M41" s="25" t="n">
-        <v>1724</v>
+        <v>3078</v>
       </c>
       <c r="N41" s="26" t="n">
         <v>0.4</v>
@@ -5950,16 +5950,16 @@
         <v>29221</v>
       </c>
       <c r="J42" s="24" t="n">
-        <v>62.5</v>
+        <v>61.1</v>
       </c>
       <c r="K42" s="24" t="n">
-        <v>50872</v>
+        <v>49732</v>
       </c>
       <c r="L42" s="25" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="M42" s="25" t="n">
-        <v>163</v>
+        <v>1302</v>
       </c>
       <c r="N42" s="26" t="n">
         <v>1.4</v>
@@ -6004,16 +6004,16 @@
         <v>58159</v>
       </c>
       <c r="J43" s="24" t="n">
-        <v>63.6</v>
+        <v>59.7</v>
       </c>
       <c r="K43" s="24" t="n">
-        <v>104784</v>
+        <v>98359</v>
       </c>
       <c r="L43" s="25" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="M43" s="25" t="n">
-        <v>1318</v>
+        <v>7743</v>
       </c>
       <c r="N43" s="26" t="n">
         <v>0.3</v>
@@ -6058,16 +6058,16 @@
         <v>1731</v>
       </c>
       <c r="J44" s="24" t="n">
-        <v>83.3</v>
+        <v>78.2</v>
       </c>
       <c r="K44" s="24" t="n">
-        <v>34328</v>
+        <v>32226</v>
       </c>
       <c r="L44" s="25" t="n">
-        <v>10.6</v>
+        <v>15.7</v>
       </c>
       <c r="M44" s="25" t="n">
-        <v>4368</v>
+        <v>6470</v>
       </c>
       <c r="N44" s="26" t="n">
         <v>1.9</v>
@@ -6112,16 +6112,16 @@
         <v>12303</v>
       </c>
       <c r="J45" s="24" t="n">
-        <v>51.7</v>
+        <v>47</v>
       </c>
       <c r="K45" s="24" t="n">
-        <v>13708</v>
+        <v>12462</v>
       </c>
       <c r="L45" s="25" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="M45" s="25" t="n">
-        <v>530</v>
+        <v>1750</v>
       </c>
       <c r="N45" s="26" t="n">
         <v>0</v>
@@ -6130,10 +6130,10 @@
         <v>0</v>
       </c>
       <c r="P45" s="27" t="n">
-        <v>53.7</v>
+        <v>53.6</v>
       </c>
       <c r="Q45" s="27" t="n">
-        <v>14239</v>
+        <v>14212</v>
       </c>
       <c r="R45" s="28" t="inlineStr">
         <is>
@@ -6166,16 +6166,16 @@
         <v>7202</v>
       </c>
       <c r="J46" s="24" t="n">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K46" s="24" t="n">
-        <v>124654</v>
+        <v>122715</v>
       </c>
       <c r="L46" s="25" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="M46" s="25" t="n">
-        <v>4571</v>
+        <v>6648</v>
       </c>
       <c r="N46" s="26" t="n">
         <v>1.5</v>
@@ -6184,10 +6184,10 @@
         <v>2078</v>
       </c>
       <c r="P46" s="27" t="n">
-        <v>94.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="Q46" s="27" t="n">
-        <v>131303</v>
+        <v>131441</v>
       </c>
       <c r="R46" s="28" t="inlineStr">
         <is>
@@ -6220,16 +6220,16 @@
         <v>186957</v>
       </c>
       <c r="J47" s="24" t="n">
-        <v>68.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="K47" s="24" t="n">
-        <v>408446</v>
+        <v>406065</v>
       </c>
       <c r="L47" s="25" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M47" s="25" t="n">
-        <v>0</v>
+        <v>1786</v>
       </c>
       <c r="N47" s="26" t="n">
         <v>0</v>
@@ -6238,10 +6238,10 @@
         <v>0</v>
       </c>
       <c r="P47" s="27" t="n">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="Q47" s="27" t="n">
-        <v>408446</v>
+        <v>407851</v>
       </c>
       <c r="R47" s="28" t="inlineStr">
         <is>
@@ -6274,16 +6274,16 @@
         <v>147864</v>
       </c>
       <c r="J48" s="24" t="n">
-        <v>60.5</v>
+        <v>59.5</v>
       </c>
       <c r="K48" s="24" t="n">
-        <v>249881</v>
+        <v>245751</v>
       </c>
       <c r="L48" s="25" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="M48" s="25" t="n">
-        <v>12391</v>
+        <v>16934</v>
       </c>
       <c r="N48" s="26" t="n">
         <v>0.7</v>
@@ -6292,10 +6292,10 @@
         <v>2891</v>
       </c>
       <c r="P48" s="27" t="n">
-        <v>64.2</v>
+        <v>64.3</v>
       </c>
       <c r="Q48" s="27" t="n">
-        <v>265163</v>
+        <v>265576</v>
       </c>
       <c r="R48" s="28" t="inlineStr">
         <is>
@@ -6328,16 +6328,16 @@
         <v>89803</v>
       </c>
       <c r="J49" s="24" t="n">
-        <v>38.3</v>
+        <v>38</v>
       </c>
       <c r="K49" s="24" t="n">
-        <v>56292</v>
+        <v>55851</v>
       </c>
       <c r="L49" s="25" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="M49" s="25" t="n">
-        <v>441</v>
+        <v>882</v>
       </c>
       <c r="N49" s="26" t="n">
         <v>0.3</v>
@@ -6382,16 +6382,16 @@
         <v>27317</v>
       </c>
       <c r="J50" s="24" t="n">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K50" s="24" t="n">
-        <v>149247</v>
+        <v>148523</v>
       </c>
       <c r="L50" s="25" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="M50" s="25" t="n">
-        <v>905</v>
+        <v>1628</v>
       </c>
       <c r="N50" s="26" t="n">
         <v>1.9</v>
@@ -6436,16 +6436,16 @@
         <v>159454</v>
       </c>
       <c r="J51" s="24" t="n">
-        <v>58.6</v>
+        <v>52.9</v>
       </c>
       <c r="K51" s="24" t="n">
-        <v>251860</v>
+        <v>227362</v>
       </c>
       <c r="L51" s="25" t="n">
-        <v>2.9</v>
+        <v>8.6</v>
       </c>
       <c r="M51" s="25" t="n">
-        <v>12464</v>
+        <v>36962</v>
       </c>
       <c r="N51" s="26" t="n">
         <v>1.4</v>
@@ -6490,16 +6490,16 @@
         <v>26177</v>
       </c>
       <c r="J52" s="24" t="n">
-        <v>64.59999999999999</v>
+        <v>60.3</v>
       </c>
       <c r="K52" s="24" t="n">
-        <v>61493</v>
+        <v>57400</v>
       </c>
       <c r="L52" s="25" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="M52" s="25" t="n">
-        <v>1618</v>
+        <v>5616</v>
       </c>
       <c r="N52" s="26" t="n">
         <v>6.2</v>
@@ -6508,10 +6508,10 @@
         <v>5902</v>
       </c>
       <c r="P52" s="27" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="Q52" s="27" t="n">
-        <v>69013</v>
+        <v>68918</v>
       </c>
       <c r="R52" s="28" t="inlineStr">
         <is>
@@ -6544,16 +6544,16 @@
         <v>4755</v>
       </c>
       <c r="J53" s="24" t="n">
-        <v>89.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K53" s="24" t="n">
-        <v>78893</v>
+        <v>73874</v>
       </c>
       <c r="L53" s="25" t="n">
-        <v>0.3</v>
+        <v>5.9</v>
       </c>
       <c r="M53" s="25" t="n">
-        <v>264</v>
+        <v>5195</v>
       </c>
       <c r="N53" s="26" t="n">
         <v>4.8</v>
@@ -6562,10 +6562,10 @@
         <v>4226</v>
       </c>
       <c r="P53" s="27" t="n">
-        <v>94.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Q53" s="27" t="n">
-        <v>83383</v>
+        <v>83295</v>
       </c>
       <c r="R53" s="28" t="inlineStr">
         <is>
@@ -6598,16 +6598,16 @@
         <v>41728</v>
       </c>
       <c r="J54" s="24" t="n">
-        <v>40.2</v>
+        <v>36.5</v>
       </c>
       <c r="K54" s="24" t="n">
-        <v>30224</v>
+        <v>27443</v>
       </c>
       <c r="L54" s="25" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="M54" s="25" t="n">
-        <v>1053</v>
+        <v>3910</v>
       </c>
       <c r="N54" s="26" t="n">
         <v>2.9</v>
@@ -6616,10 +6616,10 @@
         <v>2180</v>
       </c>
       <c r="P54" s="27" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="Q54" s="27" t="n">
-        <v>33457</v>
+        <v>33533</v>
       </c>
       <c r="R54" s="28" t="inlineStr">
         <is>
@@ -6706,16 +6706,16 @@
         <v>38771</v>
       </c>
       <c r="J56" s="24" t="n">
-        <v>54.1</v>
+        <v>52.2</v>
       </c>
       <c r="K56" s="24" t="n">
-        <v>49469</v>
+        <v>47732</v>
       </c>
       <c r="L56" s="25" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="M56" s="25" t="n">
-        <v>1372</v>
+        <v>3109</v>
       </c>
       <c r="N56" s="26" t="n">
         <v>2</v>
@@ -6760,16 +6760,16 @@
         <v>8179</v>
       </c>
       <c r="J57" s="24" t="n">
-        <v>71.40000000000001</v>
+        <v>63.7</v>
       </c>
       <c r="K57" s="24" t="n">
-        <v>32623</v>
+        <v>29105</v>
       </c>
       <c r="L57" s="25" t="n">
-        <v>2.3</v>
+        <v>9.9</v>
       </c>
       <c r="M57" s="25" t="n">
-        <v>1051</v>
+        <v>4523</v>
       </c>
       <c r="N57" s="26" t="n">
         <v>8.4</v>
@@ -6778,10 +6778,10 @@
         <v>3838</v>
       </c>
       <c r="P57" s="27" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="Q57" s="27" t="n">
-        <v>37511</v>
+        <v>37466</v>
       </c>
       <c r="R57" s="28" t="inlineStr">
         <is>
@@ -6814,16 +6814,16 @@
         <v>2286</v>
       </c>
       <c r="J58" s="24" t="n">
-        <v>76.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K58" s="24" t="n">
-        <v>18430</v>
+        <v>16866</v>
       </c>
       <c r="L58" s="25" t="n">
-        <v>12.4</v>
+        <v>18.9</v>
       </c>
       <c r="M58" s="25" t="n">
-        <v>2983</v>
+        <v>4547</v>
       </c>
       <c r="N58" s="26" t="n">
         <v>1.5</v>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="R58" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -6868,16 +6868,16 @@
         <v>44980</v>
       </c>
       <c r="J59" s="24" t="n">
-        <v>36.1</v>
+        <v>31.8</v>
       </c>
       <c r="K59" s="24" t="n">
-        <v>35609</v>
+        <v>31368</v>
       </c>
       <c r="L59" s="25" t="n">
-        <v>15.7</v>
+        <v>20</v>
       </c>
       <c r="M59" s="25" t="n">
-        <v>15486</v>
+        <v>19728</v>
       </c>
       <c r="N59" s="26" t="n">
         <v>2.6</v>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="R59" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -6922,16 +6922,16 @@
         <v>24650</v>
       </c>
       <c r="J60" s="31" t="n">
-        <v>55.3</v>
+        <v>45.2</v>
       </c>
       <c r="K60" s="31" t="n">
-        <v>32074</v>
+        <v>26216</v>
       </c>
       <c r="L60" s="32" t="n">
-        <v>1.9</v>
+        <v>12</v>
       </c>
       <c r="M60" s="32" t="n">
-        <v>1102</v>
+        <v>6960</v>
       </c>
       <c r="N60" s="33" t="n">
         <v>0.3</v>
@@ -6970,7 +6970,7 @@
   <cols>
     <col width="31" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -7077,7 +7077,7 @@
       <c r="D6" s="21" t="n"/>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>SO1606</t>
+          <t>SO2103</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -7085,42 +7085,20 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G6" s="22" t="n">
-        <v>1209</v>
-      </c>
-      <c r="H6" s="23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I6" s="23" t="n">
-        <v>111</v>
-      </c>
-      <c r="J6" s="24" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="K6" s="24" t="n">
-        <v>1035</v>
-      </c>
-      <c r="L6" s="25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="M6" s="25" t="n">
-        <v>62</v>
-      </c>
-      <c r="N6" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="27" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="Q6" s="27" t="n">
-        <v>1098</v>
-      </c>
+      <c r="G6" s="22" t="inlineStr"/>
+      <c r="H6" s="23" t="inlineStr"/>
+      <c r="I6" s="23" t="inlineStr"/>
+      <c r="J6" s="24" t="inlineStr"/>
+      <c r="K6" s="24" t="inlineStr"/>
+      <c r="L6" s="25" t="inlineStr"/>
+      <c r="M6" s="25" t="inlineStr"/>
+      <c r="N6" s="26" t="inlineStr"/>
+      <c r="O6" s="26" t="inlineStr"/>
+      <c r="P6" s="27" t="inlineStr"/>
+      <c r="Q6" s="27" t="inlineStr"/>
       <c r="R6" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7131,7 +7109,7 @@
       <c r="D7" s="21" t="n"/>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>SO2103</t>
+          <t>SO2303</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -7139,9 +7117,7 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G7" s="22" t="n">
-        <v>18977</v>
-      </c>
+      <c r="G7" s="22" t="inlineStr"/>
       <c r="H7" s="23" t="inlineStr"/>
       <c r="I7" s="23" t="inlineStr"/>
       <c r="J7" s="24" t="inlineStr"/>
@@ -7165,7 +7141,7 @@
       <c r="D8" s="21" t="n"/>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>SO2303</t>
+          <t>SO2307</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -7173,22 +7149,30 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G8" s="22" t="n">
-        <v>1518</v>
-      </c>
-      <c r="H8" s="23" t="inlineStr"/>
+      <c r="G8" s="22" t="inlineStr"/>
+      <c r="H8" s="23" t="n">
+        <v>34.5</v>
+      </c>
       <c r="I8" s="23" t="inlineStr"/>
-      <c r="J8" s="24" t="inlineStr"/>
+      <c r="J8" s="24" t="n">
+        <v>13.3</v>
+      </c>
       <c r="K8" s="24" t="inlineStr"/>
-      <c r="L8" s="25" t="inlineStr"/>
+      <c r="L8" s="25" t="n">
+        <v>49</v>
+      </c>
       <c r="M8" s="25" t="inlineStr"/>
-      <c r="N8" s="26" t="inlineStr"/>
+      <c r="N8" s="26" t="n">
+        <v>3.2</v>
+      </c>
       <c r="O8" s="26" t="inlineStr"/>
-      <c r="P8" s="27" t="inlineStr"/>
+      <c r="P8" s="27" t="n">
+        <v>65.5</v>
+      </c>
       <c r="Q8" s="27" t="inlineStr"/>
       <c r="R8" s="28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7199,7 +7183,7 @@
       <c r="D9" s="21" t="n"/>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>SO2307</t>
+          <t>SO2601</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -7207,42 +7191,30 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G9" s="22" t="n">
-        <v>13</v>
-      </c>
+      <c r="G9" s="22" t="inlineStr"/>
       <c r="H9" s="23" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="I9" s="23" t="n">
-        <v>5</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="I9" s="23" t="inlineStr"/>
       <c r="J9" s="24" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K9" s="24" t="n">
-        <v>2</v>
-      </c>
+        <v>92.8</v>
+      </c>
+      <c r="K9" s="24" t="inlineStr"/>
       <c r="L9" s="25" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="M9" s="25" t="n">
-        <v>5</v>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="M9" s="25" t="inlineStr"/>
       <c r="N9" s="26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O9" s="26" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O9" s="26" t="inlineStr"/>
       <c r="P9" s="27" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="Q9" s="27" t="n">
-        <v>8</v>
-      </c>
+        <v>99.3</v>
+      </c>
+      <c r="Q9" s="27" t="inlineStr"/>
       <c r="R9" s="28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7225,7 @@
       <c r="D10" s="21" t="n"/>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>SO2601</t>
+          <t>SO2801</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -7261,42 +7233,20 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G10" s="22" t="n">
-        <v>170643</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I10" s="23" t="n">
-        <v>1186</v>
-      </c>
-      <c r="J10" s="24" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="K10" s="24" t="n">
-        <v>167634</v>
-      </c>
-      <c r="L10" s="25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M10" s="25" t="n">
-        <v>1823</v>
-      </c>
-      <c r="N10" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="27" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="Q10" s="27" t="n">
-        <v>169457</v>
-      </c>
+      <c r="G10" s="22" t="inlineStr"/>
+      <c r="H10" s="23" t="inlineStr"/>
+      <c r="I10" s="23" t="inlineStr"/>
+      <c r="J10" s="24" t="inlineStr"/>
+      <c r="K10" s="24" t="inlineStr"/>
+      <c r="L10" s="25" t="inlineStr"/>
+      <c r="M10" s="25" t="inlineStr"/>
+      <c r="N10" s="26" t="inlineStr"/>
+      <c r="O10" s="26" t="inlineStr"/>
+      <c r="P10" s="27" t="inlineStr"/>
+      <c r="Q10" s="27" t="inlineStr"/>
       <c r="R10" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7307,7 +7257,7 @@
       <c r="D11" s="21" t="n"/>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>SO2801</t>
+          <t>SO2802</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -7315,9 +7265,7 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G11" s="22" t="n">
-        <v>0</v>
-      </c>
+      <c r="G11" s="22" t="inlineStr"/>
       <c r="H11" s="23" t="inlineStr"/>
       <c r="I11" s="23" t="inlineStr"/>
       <c r="J11" s="24" t="inlineStr"/>
@@ -7341,7 +7289,7 @@
       <c r="D12" s="21" t="n"/>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>SO2802</t>
+          <t>SO1401</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -7349,22 +7297,30 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G12" s="22" t="n">
-        <v>2253</v>
-      </c>
-      <c r="H12" s="23" t="inlineStr"/>
+      <c r="G12" s="22" t="inlineStr"/>
+      <c r="H12" s="23" t="n">
+        <v>21.7</v>
+      </c>
       <c r="I12" s="23" t="inlineStr"/>
-      <c r="J12" s="24" t="inlineStr"/>
+      <c r="J12" s="24" t="n">
+        <v>76.8</v>
+      </c>
       <c r="K12" s="24" t="inlineStr"/>
-      <c r="L12" s="25" t="inlineStr"/>
+      <c r="L12" s="25" t="n">
+        <v>1.1</v>
+      </c>
       <c r="M12" s="25" t="inlineStr"/>
-      <c r="N12" s="26" t="inlineStr"/>
+      <c r="N12" s="26" t="n">
+        <v>0.4</v>
+      </c>
       <c r="O12" s="26" t="inlineStr"/>
-      <c r="P12" s="27" t="inlineStr"/>
+      <c r="P12" s="27" t="n">
+        <v>78.3</v>
+      </c>
       <c r="Q12" s="27" t="inlineStr"/>
       <c r="R12" s="28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7331,7 @@
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>SO1401</t>
+          <t>SO1601</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -7383,39 +7339,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G13" s="22" t="n">
-        <v>16973</v>
-      </c>
+      <c r="G13" s="22" t="inlineStr"/>
       <c r="H13" s="23" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I13" s="23" t="n">
-        <v>3683</v>
-      </c>
+        <v>29.4</v>
+      </c>
+      <c r="I13" s="23" t="inlineStr"/>
       <c r="J13" s="24" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="K13" s="24" t="n">
-        <v>13035</v>
-      </c>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="K13" s="24" t="inlineStr"/>
       <c r="L13" s="25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M13" s="25" t="n">
-        <v>187</v>
-      </c>
+        <v>1.3</v>
+      </c>
+      <c r="M13" s="25" t="inlineStr"/>
       <c r="N13" s="26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O13" s="26" t="n">
-        <v>68</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="O13" s="26" t="inlineStr"/>
       <c r="P13" s="27" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="Q13" s="27" t="n">
-        <v>13289</v>
-      </c>
+        <v>70.7</v>
+      </c>
+      <c r="Q13" s="27" t="inlineStr"/>
       <c r="R13" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -7429,7 +7373,7 @@
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>SO1601</t>
+          <t>SO1606</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -7437,39 +7381,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G14" s="22" t="n">
-        <v>25482</v>
-      </c>
+      <c r="G14" s="22" t="inlineStr"/>
       <c r="H14" s="23" t="n">
         <v>29.4</v>
       </c>
-      <c r="I14" s="23" t="n">
-        <v>7492</v>
-      </c>
+      <c r="I14" s="23" t="inlineStr"/>
       <c r="J14" s="24" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="K14" s="24" t="n">
-        <v>17608</v>
-      </c>
+        <v>60.5</v>
+      </c>
+      <c r="K14" s="24" t="inlineStr"/>
       <c r="L14" s="25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M14" s="25" t="n">
-        <v>331</v>
-      </c>
+        <v>9.1</v>
+      </c>
+      <c r="M14" s="25" t="inlineStr"/>
       <c r="N14" s="26" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O14" s="26" t="n">
-        <v>76</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O14" s="26" t="inlineStr"/>
       <c r="P14" s="27" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="Q14" s="27" t="n">
-        <v>18016</v>
-      </c>
+        <v>70.59999999999999</v>
+      </c>
+      <c r="Q14" s="27" t="inlineStr"/>
       <c r="R14" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -7491,39 +7423,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G15" s="22" t="n">
-        <v>321</v>
-      </c>
+      <c r="G15" s="22" t="inlineStr"/>
       <c r="H15" s="23" t="n">
         <v>34.3</v>
       </c>
-      <c r="I15" s="23" t="n">
-        <v>110</v>
-      </c>
+      <c r="I15" s="23" t="inlineStr"/>
       <c r="J15" s="24" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>197</v>
-      </c>
+        <v>59.9</v>
+      </c>
+      <c r="K15" s="24" t="inlineStr"/>
       <c r="L15" s="25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M15" s="25" t="n">
-        <v>12</v>
-      </c>
+        <v>5.1</v>
+      </c>
+      <c r="M15" s="25" t="inlineStr"/>
       <c r="N15" s="26" t="n">
         <v>0.7</v>
       </c>
-      <c r="O15" s="26" t="n">
-        <v>2</v>
-      </c>
+      <c r="O15" s="26" t="inlineStr"/>
       <c r="P15" s="27" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="Q15" s="27" t="n">
-        <v>211</v>
-      </c>
+        <v>65.7</v>
+      </c>
+      <c r="Q15" s="27" t="inlineStr"/>
       <c r="R15" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -7545,39 +7465,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G16" s="22" t="n">
-        <v>308</v>
-      </c>
+      <c r="G16" s="22" t="inlineStr"/>
       <c r="H16" s="23" t="n">
         <v>80.3</v>
       </c>
-      <c r="I16" s="23" t="n">
-        <v>247</v>
-      </c>
+      <c r="I16" s="23" t="inlineStr"/>
       <c r="J16" s="24" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="K16" s="24" t="n">
-        <v>53</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="K16" s="24" t="inlineStr"/>
       <c r="L16" s="25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M16" s="25" t="n">
-        <v>8</v>
-      </c>
+        <v>3.7</v>
+      </c>
+      <c r="M16" s="25" t="inlineStr"/>
       <c r="N16" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="O16" s="26" t="inlineStr"/>
       <c r="P16" s="27" t="n">
         <v>19.7</v>
       </c>
-      <c r="Q16" s="27" t="n">
-        <v>61</v>
-      </c>
+      <c r="Q16" s="27" t="inlineStr"/>
       <c r="R16" s="28" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -7599,39 +7507,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G17" s="22" t="n">
-        <v>9992</v>
-      </c>
+      <c r="G17" s="22" t="inlineStr"/>
       <c r="H17" s="23" t="n">
         <v>37.9</v>
       </c>
-      <c r="I17" s="23" t="n">
-        <v>3787</v>
-      </c>
+      <c r="I17" s="23" t="inlineStr"/>
       <c r="J17" s="24" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="K17" s="24" t="n">
-        <v>5425</v>
-      </c>
+        <v>52.6</v>
+      </c>
+      <c r="K17" s="24" t="inlineStr"/>
       <c r="L17" s="25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M17" s="25" t="n">
-        <v>170</v>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="M17" s="25" t="inlineStr"/>
       <c r="N17" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="O17" s="26" t="n">
-        <v>599</v>
-      </c>
+      <c r="O17" s="26" t="inlineStr"/>
       <c r="P17" s="27" t="n">
         <v>62</v>
       </c>
-      <c r="Q17" s="27" t="n">
-        <v>6195</v>
-      </c>
+      <c r="Q17" s="27" t="inlineStr"/>
       <c r="R17" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -7653,39 +7549,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G18" s="22" t="n">
-        <v>431</v>
-      </c>
+      <c r="G18" s="22" t="inlineStr"/>
       <c r="H18" s="23" t="n">
         <v>22.1</v>
       </c>
-      <c r="I18" s="23" t="n">
-        <v>95</v>
-      </c>
+      <c r="I18" s="23" t="inlineStr"/>
       <c r="J18" s="24" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>330</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="K18" s="24" t="inlineStr"/>
       <c r="L18" s="25" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M18" s="25" t="n">
-        <v>3</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="M18" s="25" t="inlineStr"/>
       <c r="N18" s="26" t="n">
         <v>0.7</v>
       </c>
-      <c r="O18" s="26" t="n">
-        <v>3</v>
-      </c>
+      <c r="O18" s="26" t="inlineStr"/>
       <c r="P18" s="27" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="Q18" s="27" t="n">
-        <v>336</v>
-      </c>
+      <c r="Q18" s="27" t="inlineStr"/>
       <c r="R18" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -7707,39 +7591,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G19" s="22" t="n">
-        <v>0</v>
-      </c>
+      <c r="G19" s="22" t="inlineStr"/>
       <c r="H19" s="23" t="n">
         <v>22.3</v>
       </c>
-      <c r="I19" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I19" s="23" t="inlineStr"/>
       <c r="J19" s="24" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="K19" s="24" t="n">
-        <v>0</v>
-      </c>
+        <v>61.2</v>
+      </c>
+      <c r="K19" s="24" t="inlineStr"/>
       <c r="L19" s="25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="M19" s="25" t="n">
-        <v>0</v>
-      </c>
+        <v>11.3</v>
+      </c>
+      <c r="M19" s="25" t="inlineStr"/>
       <c r="N19" s="26" t="n">
         <v>5.2</v>
       </c>
-      <c r="O19" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="O19" s="26" t="inlineStr"/>
       <c r="P19" s="27" t="n">
         <v>77.7</v>
       </c>
-      <c r="Q19" s="27" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q19" s="27" t="inlineStr"/>
       <c r="R19" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -7761,39 +7633,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G20" s="22" t="n">
-        <v>0</v>
-      </c>
+      <c r="G20" s="22" t="inlineStr"/>
       <c r="H20" s="23" t="n">
         <v>49.2</v>
       </c>
-      <c r="I20" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I20" s="23" t="inlineStr"/>
       <c r="J20" s="24" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="K20" s="24" t="n">
-        <v>0</v>
-      </c>
+        <v>42.5</v>
+      </c>
+      <c r="K20" s="24" t="inlineStr"/>
       <c r="L20" s="25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M20" s="25" t="n">
-        <v>0</v>
-      </c>
+        <v>7.1</v>
+      </c>
+      <c r="M20" s="25" t="inlineStr"/>
       <c r="N20" s="26" t="n">
         <v>1.3</v>
       </c>
-      <c r="O20" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="O20" s="26" t="inlineStr"/>
       <c r="P20" s="27" t="n">
         <v>50.9</v>
       </c>
-      <c r="Q20" s="27" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q20" s="27" t="inlineStr"/>
       <c r="R20" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -7815,39 +7675,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G21" s="22" t="n">
-        <v>0</v>
-      </c>
+      <c r="G21" s="22" t="inlineStr"/>
       <c r="H21" s="23" t="n">
         <v>44.9</v>
       </c>
-      <c r="I21" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I21" s="23" t="inlineStr"/>
       <c r="J21" s="24" t="n">
         <v>54.5</v>
       </c>
-      <c r="K21" s="24" t="n">
-        <v>0</v>
-      </c>
+      <c r="K21" s="24" t="inlineStr"/>
       <c r="L21" s="25" t="n">
         <v>0.6</v>
       </c>
-      <c r="M21" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="M21" s="25" t="inlineStr"/>
       <c r="N21" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="O21" s="26" t="inlineStr"/>
       <c r="P21" s="27" t="n">
         <v>55.1</v>
       </c>
-      <c r="Q21" s="27" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q21" s="27" t="inlineStr"/>
       <c r="R21" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -7869,39 +7717,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G22" s="22" t="n">
-        <v>2979</v>
-      </c>
+      <c r="G22" s="22" t="inlineStr"/>
       <c r="H22" s="23" t="n">
         <v>43.9</v>
       </c>
-      <c r="I22" s="23" t="n">
-        <v>1308</v>
-      </c>
+      <c r="I22" s="23" t="inlineStr"/>
       <c r="J22" s="24" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="K22" s="24" t="n">
-        <v>1504</v>
-      </c>
+        <v>49.8</v>
+      </c>
+      <c r="K22" s="24" t="inlineStr"/>
       <c r="L22" s="25" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M22" s="25" t="n">
-        <v>167</v>
-      </c>
+        <v>6.2</v>
+      </c>
+      <c r="M22" s="25" t="inlineStr"/>
       <c r="N22" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O22" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="O22" s="26" t="inlineStr"/>
       <c r="P22" s="27" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="Q22" s="27" t="n">
-        <v>1671</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="Q22" s="27" t="inlineStr"/>
       <c r="R22" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -7923,39 +7759,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G23" s="22" t="n">
-        <v>9291</v>
-      </c>
+      <c r="G23" s="22" t="inlineStr"/>
       <c r="H23" s="23" t="n">
         <v>40.4</v>
       </c>
-      <c r="I23" s="23" t="n">
-        <v>3753</v>
-      </c>
+      <c r="I23" s="23" t="inlineStr"/>
       <c r="J23" s="24" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="K23" s="24" t="n">
-        <v>5370</v>
-      </c>
+        <v>56.7</v>
+      </c>
+      <c r="K23" s="24" t="inlineStr"/>
       <c r="L23" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M23" s="25" t="n">
-        <v>139</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="M23" s="25" t="inlineStr"/>
       <c r="N23" s="26" t="n">
         <v>0.4</v>
       </c>
-      <c r="O23" s="26" t="n">
-        <v>37</v>
-      </c>
+      <c r="O23" s="26" t="inlineStr"/>
       <c r="P23" s="27" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="Q23" s="27" t="n">
-        <v>5547</v>
-      </c>
+        <v>59.6</v>
+      </c>
+      <c r="Q23" s="27" t="inlineStr"/>
       <c r="R23" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -7977,39 +7801,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G24" s="22" t="n">
-        <v>294</v>
-      </c>
+      <c r="G24" s="22" t="inlineStr"/>
       <c r="H24" s="23" t="n">
         <v>48.3</v>
       </c>
-      <c r="I24" s="23" t="n">
-        <v>142</v>
-      </c>
+      <c r="I24" s="23" t="inlineStr"/>
       <c r="J24" s="24" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="K24" s="24" t="n">
-        <v>145</v>
-      </c>
+        <v>49.3</v>
+      </c>
+      <c r="K24" s="24" t="inlineStr"/>
       <c r="L24" s="25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M24" s="25" t="n">
-        <v>1</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="M24" s="25" t="inlineStr"/>
       <c r="N24" s="26" t="n">
         <v>1.9</v>
       </c>
-      <c r="O24" s="26" t="n">
-        <v>6</v>
-      </c>
+      <c r="O24" s="26" t="inlineStr"/>
       <c r="P24" s="27" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="Q24" s="27" t="n">
-        <v>152</v>
-      </c>
+        <v>51.7</v>
+      </c>
+      <c r="Q24" s="27" t="inlineStr"/>
       <c r="R24" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8031,39 +7843,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G25" s="22" t="n">
-        <v>4648</v>
-      </c>
+      <c r="G25" s="22" t="inlineStr"/>
       <c r="H25" s="23" t="n">
         <v>17.9</v>
       </c>
-      <c r="I25" s="23" t="n">
-        <v>832</v>
-      </c>
+      <c r="I25" s="23" t="inlineStr"/>
       <c r="J25" s="24" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="K25" s="24" t="n">
-        <v>3691</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="K25" s="24" t="inlineStr"/>
       <c r="L25" s="25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M25" s="25" t="n">
-        <v>126</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="M25" s="25" t="inlineStr"/>
       <c r="N25" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="O25" s="26" t="inlineStr"/>
       <c r="P25" s="27" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="Q25" s="27" t="n">
-        <v>3816</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="Q25" s="27" t="inlineStr"/>
       <c r="R25" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8085,39 +7885,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G26" s="22" t="n">
-        <v>617</v>
-      </c>
+      <c r="G26" s="22" t="inlineStr"/>
       <c r="H26" s="23" t="n">
         <v>23.1</v>
       </c>
-      <c r="I26" s="23" t="n">
-        <v>143</v>
-      </c>
+      <c r="I26" s="23" t="inlineStr"/>
       <c r="J26" s="24" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="K26" s="24" t="n">
-        <v>459</v>
-      </c>
+        <v>69.2</v>
+      </c>
+      <c r="K26" s="24" t="inlineStr"/>
       <c r="L26" s="25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M26" s="25" t="n">
-        <v>8</v>
-      </c>
+        <v>6.4</v>
+      </c>
+      <c r="M26" s="25" t="inlineStr"/>
       <c r="N26" s="26" t="n">
         <v>1.3</v>
       </c>
-      <c r="O26" s="26" t="n">
-        <v>8</v>
-      </c>
+      <c r="O26" s="26" t="inlineStr"/>
       <c r="P26" s="27" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q26" s="27" t="n">
-        <v>475</v>
-      </c>
+        <v>76.90000000000001</v>
+      </c>
+      <c r="Q26" s="27" t="inlineStr"/>
       <c r="R26" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8139,39 +7927,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G27" s="22" t="n">
-        <v>720</v>
-      </c>
+      <c r="G27" s="22" t="inlineStr"/>
       <c r="H27" s="23" t="n">
         <v>0.9</v>
       </c>
-      <c r="I27" s="23" t="n">
-        <v>6</v>
-      </c>
+      <c r="I27" s="23" t="inlineStr"/>
       <c r="J27" s="24" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="K27" s="24" t="n">
-        <v>676</v>
-      </c>
+        <v>90.3</v>
+      </c>
+      <c r="K27" s="24" t="inlineStr"/>
       <c r="L27" s="25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M27" s="25" t="n">
-        <v>25</v>
-      </c>
+        <v>7.1</v>
+      </c>
+      <c r="M27" s="25" t="inlineStr"/>
       <c r="N27" s="26" t="n">
         <v>1.8</v>
       </c>
-      <c r="O27" s="26" t="n">
-        <v>13</v>
-      </c>
+      <c r="O27" s="26" t="inlineStr"/>
       <c r="P27" s="27" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="Q27" s="27" t="n">
-        <v>714</v>
-      </c>
+        <v>99.2</v>
+      </c>
+      <c r="Q27" s="27" t="inlineStr"/>
       <c r="R27" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8193,39 +7969,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G28" s="22" t="n">
-        <v>0</v>
-      </c>
+      <c r="G28" s="22" t="inlineStr"/>
       <c r="H28" s="23" t="n">
         <v>1.4</v>
       </c>
-      <c r="I28" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I28" s="23" t="inlineStr"/>
       <c r="J28" s="24" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="K28" s="24" t="n">
-        <v>0</v>
-      </c>
+        <v>91.7</v>
+      </c>
+      <c r="K28" s="24" t="inlineStr"/>
       <c r="L28" s="25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M28" s="25" t="n">
-        <v>0</v>
-      </c>
+        <v>6.6</v>
+      </c>
+      <c r="M28" s="25" t="inlineStr"/>
       <c r="N28" s="26" t="n">
         <v>0.3</v>
       </c>
-      <c r="O28" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="O28" s="26" t="inlineStr"/>
       <c r="P28" s="27" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="Q28" s="27" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q28" s="27" t="inlineStr"/>
       <c r="R28" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8247,39 +8011,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G29" s="22" t="n">
-        <v>0</v>
-      </c>
+      <c r="G29" s="22" t="inlineStr"/>
       <c r="H29" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="I29" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I29" s="23" t="inlineStr"/>
       <c r="J29" s="24" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="K29" s="24" t="n">
-        <v>0</v>
-      </c>
+        <v>88.2</v>
+      </c>
+      <c r="K29" s="24" t="inlineStr"/>
       <c r="L29" s="25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M29" s="25" t="n">
-        <v>0</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="M29" s="25" t="inlineStr"/>
       <c r="N29" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O29" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="O29" s="26" t="inlineStr"/>
       <c r="P29" s="27" t="n">
         <v>89</v>
       </c>
-      <c r="Q29" s="27" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q29" s="27" t="inlineStr"/>
       <c r="R29" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8301,39 +8053,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G30" s="22" t="n">
-        <v>0</v>
-      </c>
+      <c r="G30" s="22" t="inlineStr"/>
       <c r="H30" s="23" t="n">
         <v>9.1</v>
       </c>
-      <c r="I30" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I30" s="23" t="inlineStr"/>
       <c r="J30" s="24" t="n">
         <v>88</v>
       </c>
-      <c r="K30" s="24" t="n">
-        <v>0</v>
-      </c>
+      <c r="K30" s="24" t="inlineStr"/>
       <c r="L30" s="25" t="n">
         <v>2.9</v>
       </c>
-      <c r="M30" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="M30" s="25" t="inlineStr"/>
       <c r="N30" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="O30" s="26" t="inlineStr"/>
       <c r="P30" s="27" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="Q30" s="27" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q30" s="27" t="inlineStr"/>
       <c r="R30" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8355,39 +8095,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G31" s="22" t="n">
-        <v>35363</v>
-      </c>
+      <c r="G31" s="22" t="inlineStr"/>
       <c r="H31" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I31" s="23" t="inlineStr"/>
       <c r="J31" s="24" t="n">
         <v>100</v>
       </c>
-      <c r="K31" s="24" t="n">
-        <v>35363</v>
-      </c>
+      <c r="K31" s="24" t="inlineStr"/>
       <c r="L31" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="M31" s="25" t="inlineStr"/>
       <c r="N31" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="O31" s="26" t="inlineStr"/>
       <c r="P31" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="Q31" s="27" t="n">
-        <v>35363</v>
-      </c>
+      <c r="Q31" s="27" t="inlineStr"/>
       <c r="R31" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8409,39 +8137,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G32" s="22" t="n">
-        <v>914</v>
-      </c>
+      <c r="G32" s="22" t="inlineStr"/>
       <c r="H32" s="23" t="n">
         <v>1.4</v>
       </c>
-      <c r="I32" s="23" t="n">
-        <v>13</v>
-      </c>
+      <c r="I32" s="23" t="inlineStr"/>
       <c r="J32" s="24" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="K32" s="24" t="n">
-        <v>894</v>
-      </c>
+        <v>97.09999999999999</v>
+      </c>
+      <c r="K32" s="24" t="inlineStr"/>
       <c r="L32" s="25" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M32" s="25" t="n">
-        <v>6</v>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="M32" s="25" t="inlineStr"/>
       <c r="N32" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="O32" s="26" t="inlineStr"/>
       <c r="P32" s="27" t="n">
         <v>98.5</v>
       </c>
-      <c r="Q32" s="27" t="n">
-        <v>901</v>
-      </c>
+      <c r="Q32" s="27" t="inlineStr"/>
       <c r="R32" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8463,39 +8179,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G33" s="22" t="n">
-        <v>343268</v>
-      </c>
+      <c r="G33" s="22" t="inlineStr"/>
       <c r="H33" s="23" t="n">
         <v>24.7</v>
       </c>
-      <c r="I33" s="23" t="n">
-        <v>84787</v>
-      </c>
+      <c r="I33" s="23" t="inlineStr"/>
       <c r="J33" s="24" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="K33" s="24" t="n">
-        <v>249556</v>
-      </c>
+        <v>71.09999999999999</v>
+      </c>
+      <c r="K33" s="24" t="inlineStr"/>
       <c r="L33" s="25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M33" s="25" t="n">
-        <v>8925</v>
-      </c>
+        <v>4.1</v>
+      </c>
+      <c r="M33" s="25" t="inlineStr"/>
       <c r="N33" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="O33" s="26" t="inlineStr"/>
       <c r="P33" s="27" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="Q33" s="27" t="n">
-        <v>258481</v>
-      </c>
+        <v>75.2</v>
+      </c>
+      <c r="Q33" s="27" t="inlineStr"/>
       <c r="R33" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8517,39 +8221,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G34" s="22" t="n">
-        <v>1648</v>
-      </c>
+      <c r="G34" s="22" t="inlineStr"/>
       <c r="H34" s="23" t="n">
         <v>0.6</v>
       </c>
-      <c r="I34" s="23" t="n">
-        <v>10</v>
-      </c>
+      <c r="I34" s="23" t="inlineStr"/>
       <c r="J34" s="24" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="K34" s="24" t="n">
-        <v>1630</v>
-      </c>
+      <c r="K34" s="24" t="inlineStr"/>
       <c r="L34" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="M34" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="M34" s="25" t="inlineStr"/>
       <c r="N34" s="26" t="n">
         <v>0.6</v>
       </c>
-      <c r="O34" s="26" t="n">
-        <v>10</v>
-      </c>
+      <c r="O34" s="26" t="inlineStr"/>
       <c r="P34" s="27" t="n">
         <v>99.5</v>
       </c>
-      <c r="Q34" s="27" t="n">
-        <v>1640</v>
-      </c>
+      <c r="Q34" s="27" t="inlineStr"/>
       <c r="R34" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8571,39 +8263,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G35" s="22" t="n">
-        <v>23402</v>
-      </c>
+      <c r="G35" s="22" t="inlineStr"/>
       <c r="H35" s="23" t="n">
         <v>3.9</v>
       </c>
-      <c r="I35" s="23" t="n">
-        <v>913</v>
-      </c>
+      <c r="I35" s="23" t="inlineStr"/>
       <c r="J35" s="24" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="K35" s="24" t="n">
-        <v>21320</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="K35" s="24" t="inlineStr"/>
       <c r="L35" s="25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M35" s="25" t="n">
-        <v>959</v>
-      </c>
+        <v>5.2</v>
+      </c>
+      <c r="M35" s="25" t="inlineStr"/>
       <c r="N35" s="26" t="n">
         <v>0.8</v>
       </c>
-      <c r="O35" s="26" t="n">
-        <v>187</v>
-      </c>
+      <c r="O35" s="26" t="inlineStr"/>
       <c r="P35" s="27" t="n">
         <v>96</v>
       </c>
-      <c r="Q35" s="27" t="n">
-        <v>22466</v>
-      </c>
+      <c r="Q35" s="27" t="inlineStr"/>
       <c r="R35" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8625,39 +8305,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G36" s="22" t="n">
-        <v>3132</v>
-      </c>
+      <c r="G36" s="22" t="inlineStr"/>
       <c r="H36" s="23" t="n">
         <v>16.5</v>
       </c>
-      <c r="I36" s="23" t="n">
-        <v>517</v>
-      </c>
+      <c r="I36" s="23" t="inlineStr"/>
       <c r="J36" s="24" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="K36" s="24" t="n">
-        <v>2346</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="K36" s="24" t="inlineStr"/>
       <c r="L36" s="25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M36" s="25" t="n">
-        <v>19</v>
-      </c>
+        <v>8.6</v>
+      </c>
+      <c r="M36" s="25" t="inlineStr"/>
       <c r="N36" s="26" t="n">
         <v>7.9</v>
       </c>
-      <c r="O36" s="26" t="n">
-        <v>247</v>
-      </c>
+      <c r="O36" s="26" t="inlineStr"/>
       <c r="P36" s="27" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="Q36" s="27" t="n">
-        <v>2612</v>
-      </c>
+        <v>83.5</v>
+      </c>
+      <c r="Q36" s="27" t="inlineStr"/>
       <c r="R36" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8679,39 +8347,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G37" s="22" t="n">
-        <v>0</v>
-      </c>
+      <c r="G37" s="22" t="inlineStr"/>
       <c r="H37" s="23" t="n">
         <v>48.5</v>
       </c>
-      <c r="I37" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I37" s="23" t="inlineStr"/>
       <c r="J37" s="24" t="n">
         <v>51.5</v>
       </c>
-      <c r="K37" s="24" t="n">
-        <v>0</v>
-      </c>
+      <c r="K37" s="24" t="inlineStr"/>
       <c r="L37" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="M37" s="25" t="n">
-        <v>0</v>
-      </c>
+      <c r="M37" s="25" t="inlineStr"/>
       <c r="N37" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="O37" s="26" t="inlineStr"/>
       <c r="P37" s="27" t="n">
         <v>51.5</v>
       </c>
-      <c r="Q37" s="27" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q37" s="27" t="inlineStr"/>
       <c r="R37" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8733,39 +8389,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G38" s="22" t="n">
-        <v>752</v>
-      </c>
+      <c r="G38" s="22" t="inlineStr"/>
       <c r="H38" s="23" t="n">
         <v>25.6</v>
       </c>
-      <c r="I38" s="23" t="n">
-        <v>193</v>
-      </c>
+      <c r="I38" s="23" t="inlineStr"/>
       <c r="J38" s="24" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="K38" s="24" t="n">
-        <v>499</v>
-      </c>
+        <v>63.8</v>
+      </c>
+      <c r="K38" s="24" t="inlineStr"/>
       <c r="L38" s="25" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="M38" s="25" t="n">
-        <v>52</v>
-      </c>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="M38" s="25" t="inlineStr"/>
       <c r="N38" s="26" t="n">
         <v>1.2</v>
       </c>
-      <c r="O38" s="26" t="n">
-        <v>9</v>
-      </c>
+      <c r="O38" s="26" t="inlineStr"/>
       <c r="P38" s="27" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="Q38" s="27" t="n">
-        <v>560</v>
-      </c>
+        <v>74.3</v>
+      </c>
+      <c r="Q38" s="27" t="inlineStr"/>
       <c r="R38" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8787,39 +8431,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G39" s="22" t="n">
-        <v>4993</v>
-      </c>
+      <c r="G39" s="22" t="inlineStr"/>
       <c r="H39" s="23" t="n">
         <v>3.1</v>
       </c>
-      <c r="I39" s="23" t="n">
-        <v>155</v>
-      </c>
+      <c r="I39" s="23" t="inlineStr"/>
       <c r="J39" s="24" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="K39" s="24" t="n">
-        <v>4499</v>
-      </c>
+        <v>82.7</v>
+      </c>
+      <c r="K39" s="24" t="inlineStr"/>
       <c r="L39" s="25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M39" s="25" t="n">
-        <v>95</v>
-      </c>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="M39" s="25" t="inlineStr"/>
       <c r="N39" s="26" t="n">
         <v>4.9</v>
       </c>
-      <c r="O39" s="26" t="n">
-        <v>245</v>
-      </c>
+      <c r="O39" s="26" t="inlineStr"/>
       <c r="P39" s="27" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="Q39" s="27" t="n">
-        <v>4839</v>
-      </c>
+      <c r="Q39" s="27" t="inlineStr"/>
       <c r="R39" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8841,39 +8473,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G40" s="22" t="n">
-        <v>12638</v>
-      </c>
+      <c r="G40" s="22" t="inlineStr"/>
       <c r="H40" s="23" t="n">
         <v>1.1</v>
       </c>
-      <c r="I40" s="23" t="n">
-        <v>139</v>
-      </c>
+      <c r="I40" s="23" t="inlineStr"/>
       <c r="J40" s="24" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="K40" s="24" t="n">
-        <v>12360</v>
-      </c>
+        <v>92.2</v>
+      </c>
+      <c r="K40" s="24" t="inlineStr"/>
       <c r="L40" s="25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M40" s="25" t="n">
-        <v>139</v>
-      </c>
+        <v>6.7</v>
+      </c>
+      <c r="M40" s="25" t="inlineStr"/>
       <c r="N40" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="26" t="n">
-        <v>0</v>
-      </c>
+      <c r="O40" s="26" t="inlineStr"/>
       <c r="P40" s="27" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="Q40" s="27" t="n">
-        <v>12499</v>
-      </c>
+      <c r="Q40" s="27" t="inlineStr"/>
       <c r="R40" s="28" t="inlineStr">
         <is>
           <t>3</t>
@@ -8895,39 +8515,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G41" s="22" t="n">
-        <v>2600</v>
-      </c>
+      <c r="G41" s="22" t="inlineStr"/>
       <c r="H41" s="23" t="n">
         <v>36.3</v>
       </c>
-      <c r="I41" s="23" t="n">
-        <v>944</v>
-      </c>
+      <c r="I41" s="23" t="inlineStr"/>
       <c r="J41" s="24" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="K41" s="24" t="n">
-        <v>1105</v>
-      </c>
+        <v>31.8</v>
+      </c>
+      <c r="K41" s="24" t="inlineStr"/>
       <c r="L41" s="25" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="M41" s="25" t="n">
-        <v>523</v>
-      </c>
+        <v>30.7</v>
+      </c>
+      <c r="M41" s="25" t="inlineStr"/>
       <c r="N41" s="26" t="n">
         <v>1.1</v>
       </c>
-      <c r="O41" s="26" t="n">
-        <v>29</v>
-      </c>
+      <c r="O41" s="26" t="inlineStr"/>
       <c r="P41" s="27" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="Q41" s="27" t="n">
-        <v>1656</v>
-      </c>
+        <v>63.6</v>
+      </c>
+      <c r="Q41" s="27" t="inlineStr"/>
       <c r="R41" s="28" t="inlineStr">
         <is>
           <t>4</t>
@@ -8949,39 +8557,27 @@
           <t>recent_idp</t>
         </is>
       </c>
-      <c r="G42" s="29" t="n">
-        <v>3610</v>
-      </c>
+      <c r="G42" s="29" t="inlineStr"/>
       <c r="H42" s="30" t="n">
         <v>11.7</v>
       </c>
-      <c r="I42" s="30" t="n">
-        <v>422</v>
-      </c>
+      <c r="I42" s="30" t="inlineStr"/>
       <c r="J42" s="31" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="K42" s="31" t="n">
-        <v>3152</v>
-      </c>
+        <v>81.3</v>
+      </c>
+      <c r="K42" s="31" t="inlineStr"/>
       <c r="L42" s="32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M42" s="32" t="n">
-        <v>40</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="M42" s="32" t="inlineStr"/>
       <c r="N42" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="O42" s="33" t="n">
-        <v>0</v>
-      </c>
+      <c r="O42" s="33" t="inlineStr"/>
       <c r="P42" s="34" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="Q42" s="34" t="n">
-        <v>3191</v>
-      </c>
+        <v>88.3</v>
+      </c>
+      <c r="Q42" s="34" t="inlineStr"/>
       <c r="R42" s="28" t="inlineStr">
         <is>
           <t>3</t>

--- a/platform_PiN_output/Somalia___SOM/PiN_step2_Somalia___SOM_1022_08AM.xlsx
+++ b/platform_PiN_output/Somalia___SOM/PiN_step2_Somalia___SOM_1022_08AM.xlsx
@@ -10,7 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PiN TOTAL" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall PiN and severity" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PiN -- affected_pop" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PiN -- recent_idp" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -604,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="3" max="3"/>
@@ -867,71 +866,41 @@
     <row r="8">
       <c r="A8" s="2" t="n"/>
       <c r="B8" s="2" t="n"/>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>recent_idp (5-17 y.o.)</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>0</v>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Girls (5-17 y.o.)</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>All population groups</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>1958712</v>
       </c>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>recent_idp (5-17 y.o.)</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="11" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="11" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="11" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="11" t="n">
-        <v/>
-      </c>
-      <c r="T8" s="11" t="n">
-        <v>0</v>
-      </c>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n"/>
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Girls (5-17 y.o.)</t>
+          <t>Boys (5-17 y.o.)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -940,7 +909,7 @@
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>1958712</v>
+        <v>2121938</v>
       </c>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
@@ -961,18 +930,18 @@
     <row r="10">
       <c r="A10" s="2" t="n"/>
       <c r="B10" s="2" t="n"/>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Boys (5-17 y.o.)</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>ECE (5 y.o.)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>All population groups</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
-        <v>2121938</v>
+      <c r="E10" s="13" t="n">
+        <v>313896</v>
       </c>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
@@ -995,7 +964,7 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>ECE (5 y.o.)</t>
+          <t>Children with disability</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
@@ -1004,7 +973,7 @@
         </is>
       </c>
       <c r="E11" s="13" t="n">
-        <v>313896</v>
+        <v>408065</v>
       </c>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
@@ -1021,38 +990,6 @@
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="2" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Children with disability</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>All population groups</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="n">
-        <v>408065</v>
-      </c>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
-      <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2" t="n"/>
-      <c r="R12" s="2" t="n"/>
-      <c r="S12" s="2" t="n"/>
-      <c r="T12" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6957,1637 +6894,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="33" customWidth="1" min="16" max="16"/>
-    <col width="33" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>PiN -- recent_idp (5-17 y.o.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5">
-      <c r="A5" s="14" t="n"/>
-      <c r="B5" s="14" t="n"/>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>Admin Pcode</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>Population group</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>TotN</t>
-        </is>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
-        <is>
-          <t>% severity levels 1-2</t>
-        </is>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t># severity levels 1-2</t>
-        </is>
-      </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t>% severity level 3</t>
-        </is>
-      </c>
-      <c r="K5" s="17" t="inlineStr">
-        <is>
-          <t># severity level 3</t>
-        </is>
-      </c>
-      <c r="L5" s="18" t="inlineStr">
-        <is>
-          <t>% severity level 4</t>
-        </is>
-      </c>
-      <c r="M5" s="18" t="inlineStr">
-        <is>
-          <t># severity level 4</t>
-        </is>
-      </c>
-      <c r="N5" s="19" t="inlineStr">
-        <is>
-          <t>% severity level 5</t>
-        </is>
-      </c>
-      <c r="O5" s="19" t="inlineStr">
-        <is>
-          <t># severity level 5</t>
-        </is>
-      </c>
-      <c r="P5" s="20" t="inlineStr">
-        <is>
-          <t>% Tot PiN (severity levels 3-5)</t>
-        </is>
-      </c>
-      <c r="Q5" s="20" t="inlineStr">
-        <is>
-          <t># Tot PiN (severity levels 3-5)</t>
-        </is>
-      </c>
-      <c r="R5" s="20" t="inlineStr">
-        <is>
-          <t>Area severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="21" t="n"/>
-      <c r="B6" s="21" t="n"/>
-      <c r="C6" s="21" t="n"/>
-      <c r="D6" s="21" t="n"/>
-      <c r="E6" s="22" t="inlineStr">
-        <is>
-          <t>SO2103</t>
-        </is>
-      </c>
-      <c r="F6" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G6" s="22" t="inlineStr"/>
-      <c r="H6" s="23" t="inlineStr"/>
-      <c r="I6" s="23" t="inlineStr"/>
-      <c r="J6" s="24" t="inlineStr"/>
-      <c r="K6" s="24" t="inlineStr"/>
-      <c r="L6" s="25" t="inlineStr"/>
-      <c r="M6" s="25" t="inlineStr"/>
-      <c r="N6" s="26" t="inlineStr"/>
-      <c r="O6" s="26" t="inlineStr"/>
-      <c r="P6" s="27" t="inlineStr"/>
-      <c r="Q6" s="27" t="inlineStr"/>
-      <c r="R6" s="28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="n"/>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="22" t="inlineStr">
-        <is>
-          <t>SO2303</t>
-        </is>
-      </c>
-      <c r="F7" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G7" s="22" t="inlineStr"/>
-      <c r="H7" s="23" t="inlineStr"/>
-      <c r="I7" s="23" t="inlineStr"/>
-      <c r="J7" s="24" t="inlineStr"/>
-      <c r="K7" s="24" t="inlineStr"/>
-      <c r="L7" s="25" t="inlineStr"/>
-      <c r="M7" s="25" t="inlineStr"/>
-      <c r="N7" s="26" t="inlineStr"/>
-      <c r="O7" s="26" t="inlineStr"/>
-      <c r="P7" s="27" t="inlineStr"/>
-      <c r="Q7" s="27" t="inlineStr"/>
-      <c r="R7" s="28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="21" t="n"/>
-      <c r="B8" s="21" t="n"/>
-      <c r="C8" s="21" t="n"/>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>SO2307</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G8" s="22" t="inlineStr"/>
-      <c r="H8" s="23" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="I8" s="23" t="inlineStr"/>
-      <c r="J8" s="24" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="K8" s="24" t="inlineStr"/>
-      <c r="L8" s="25" t="n">
-        <v>49</v>
-      </c>
-      <c r="M8" s="25" t="inlineStr"/>
-      <c r="N8" s="26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O8" s="26" t="inlineStr"/>
-      <c r="P8" s="27" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="Q8" s="27" t="inlineStr"/>
-      <c r="R8" s="28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="21" t="n"/>
-      <c r="B9" s="21" t="n"/>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>SO2601</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G9" s="22" t="inlineStr"/>
-      <c r="H9" s="23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I9" s="23" t="inlineStr"/>
-      <c r="J9" s="24" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="K9" s="24" t="inlineStr"/>
-      <c r="L9" s="25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M9" s="25" t="inlineStr"/>
-      <c r="N9" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="26" t="inlineStr"/>
-      <c r="P9" s="27" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="Q9" s="27" t="inlineStr"/>
-      <c r="R9" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="21" t="n"/>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>SO2801</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G10" s="22" t="inlineStr"/>
-      <c r="H10" s="23" t="inlineStr"/>
-      <c r="I10" s="23" t="inlineStr"/>
-      <c r="J10" s="24" t="inlineStr"/>
-      <c r="K10" s="24" t="inlineStr"/>
-      <c r="L10" s="25" t="inlineStr"/>
-      <c r="M10" s="25" t="inlineStr"/>
-      <c r="N10" s="26" t="inlineStr"/>
-      <c r="O10" s="26" t="inlineStr"/>
-      <c r="P10" s="27" t="inlineStr"/>
-      <c r="Q10" s="27" t="inlineStr"/>
-      <c r="R10" s="28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="21" t="n"/>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>SO2802</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G11" s="22" t="inlineStr"/>
-      <c r="H11" s="23" t="inlineStr"/>
-      <c r="I11" s="23" t="inlineStr"/>
-      <c r="J11" s="24" t="inlineStr"/>
-      <c r="K11" s="24" t="inlineStr"/>
-      <c r="L11" s="25" t="inlineStr"/>
-      <c r="M11" s="25" t="inlineStr"/>
-      <c r="N11" s="26" t="inlineStr"/>
-      <c r="O11" s="26" t="inlineStr"/>
-      <c r="P11" s="27" t="inlineStr"/>
-      <c r="Q11" s="27" t="inlineStr"/>
-      <c r="R11" s="28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="n"/>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="22" t="inlineStr">
-        <is>
-          <t>SO1401</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G12" s="22" t="inlineStr"/>
-      <c r="H12" s="23" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I12" s="23" t="inlineStr"/>
-      <c r="J12" s="24" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="K12" s="24" t="inlineStr"/>
-      <c r="L12" s="25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M12" s="25" t="inlineStr"/>
-      <c r="N12" s="26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O12" s="26" t="inlineStr"/>
-      <c r="P12" s="27" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="Q12" s="27" t="inlineStr"/>
-      <c r="R12" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="n"/>
-      <c r="B13" s="21" t="n"/>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>SO1601</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="inlineStr"/>
-      <c r="H13" s="23" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="I13" s="23" t="inlineStr"/>
-      <c r="J13" s="24" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="K13" s="24" t="inlineStr"/>
-      <c r="L13" s="25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M13" s="25" t="inlineStr"/>
-      <c r="N13" s="26" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O13" s="26" t="inlineStr"/>
-      <c r="P13" s="27" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="Q13" s="27" t="inlineStr"/>
-      <c r="R13" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="n"/>
-      <c r="B14" s="21" t="n"/>
-      <c r="C14" s="21" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>SO1606</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G14" s="22" t="inlineStr"/>
-      <c r="H14" s="23" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="I14" s="23" t="inlineStr"/>
-      <c r="J14" s="24" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="K14" s="24" t="inlineStr"/>
-      <c r="L14" s="25" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="M14" s="25" t="inlineStr"/>
-      <c r="N14" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" s="26" t="inlineStr"/>
-      <c r="P14" s="27" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="Q14" s="27" t="inlineStr"/>
-      <c r="R14" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="n"/>
-      <c r="B15" s="21" t="n"/>
-      <c r="C15" s="21" t="n"/>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>SO1103</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G15" s="22" t="inlineStr"/>
-      <c r="H15" s="23" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr"/>
-      <c r="J15" s="24" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="K15" s="24" t="inlineStr"/>
-      <c r="L15" s="25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M15" s="25" t="inlineStr"/>
-      <c r="N15" s="26" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O15" s="26" t="inlineStr"/>
-      <c r="P15" s="27" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="Q15" s="27" t="inlineStr"/>
-      <c r="R15" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="n"/>
-      <c r="B16" s="21" t="n"/>
-      <c r="C16" s="21" t="n"/>
-      <c r="D16" s="21" t="n"/>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>SO1202</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="inlineStr"/>
-      <c r="H16" s="23" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="I16" s="23" t="inlineStr"/>
-      <c r="J16" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="K16" s="24" t="inlineStr"/>
-      <c r="L16" s="25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M16" s="25" t="inlineStr"/>
-      <c r="N16" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="26" t="inlineStr"/>
-      <c r="P16" s="27" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="Q16" s="27" t="inlineStr"/>
-      <c r="R16" s="28" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="n"/>
-      <c r="B17" s="21" t="n"/>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>SO1501</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="inlineStr"/>
-      <c r="H17" s="23" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="I17" s="23" t="inlineStr"/>
-      <c r="J17" s="24" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="K17" s="24" t="inlineStr"/>
-      <c r="L17" s="25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M17" s="25" t="inlineStr"/>
-      <c r="N17" s="26" t="n">
-        <v>6</v>
-      </c>
-      <c r="O17" s="26" t="inlineStr"/>
-      <c r="P17" s="27" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q17" s="27" t="inlineStr"/>
-      <c r="R17" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="n"/>
-      <c r="B18" s="21" t="n"/>
-      <c r="C18" s="21" t="n"/>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>SO1701</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="inlineStr"/>
-      <c r="H18" s="23" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="I18" s="23" t="inlineStr"/>
-      <c r="J18" s="24" t="n">
-        <v>75</v>
-      </c>
-      <c r="K18" s="24" t="inlineStr"/>
-      <c r="L18" s="25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M18" s="25" t="inlineStr"/>
-      <c r="N18" s="26" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O18" s="26" t="inlineStr"/>
-      <c r="P18" s="27" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="Q18" s="27" t="inlineStr"/>
-      <c r="R18" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n"/>
-      <c r="B19" s="21" t="n"/>
-      <c r="C19" s="21" t="n"/>
-      <c r="D19" s="21" t="n"/>
-      <c r="E19" s="22" t="inlineStr">
-        <is>
-          <t>SO1801</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G19" s="22" t="inlineStr"/>
-      <c r="H19" s="23" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I19" s="23" t="inlineStr"/>
-      <c r="J19" s="24" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="K19" s="24" t="inlineStr"/>
-      <c r="L19" s="25" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M19" s="25" t="inlineStr"/>
-      <c r="N19" s="26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O19" s="26" t="inlineStr"/>
-      <c r="P19" s="27" t="n">
-        <v>77.7</v>
-      </c>
-      <c r="Q19" s="27" t="inlineStr"/>
-      <c r="R19" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="n"/>
-      <c r="B20" s="21" t="n"/>
-      <c r="C20" s="21" t="n"/>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="22" t="inlineStr">
-        <is>
-          <t>SO1802</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="inlineStr"/>
-      <c r="H20" s="23" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="I20" s="23" t="inlineStr"/>
-      <c r="J20" s="24" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="K20" s="24" t="inlineStr"/>
-      <c r="L20" s="25" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="M20" s="25" t="inlineStr"/>
-      <c r="N20" s="26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O20" s="26" t="inlineStr"/>
-      <c r="P20" s="27" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="Q20" s="27" t="inlineStr"/>
-      <c r="R20" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="n"/>
-      <c r="B21" s="21" t="n"/>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="21" t="n"/>
-      <c r="E21" s="22" t="inlineStr">
-        <is>
-          <t>SO1803</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G21" s="22" t="inlineStr"/>
-      <c r="H21" s="23" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="I21" s="23" t="inlineStr"/>
-      <c r="J21" s="24" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="K21" s="24" t="inlineStr"/>
-      <c r="L21" s="25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M21" s="25" t="inlineStr"/>
-      <c r="N21" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="26" t="inlineStr"/>
-      <c r="P21" s="27" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="Q21" s="27" t="inlineStr"/>
-      <c r="R21" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="21" t="n"/>
-      <c r="B22" s="21" t="n"/>
-      <c r="C22" s="21" t="n"/>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>SO1901</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G22" s="22" t="inlineStr"/>
-      <c r="H22" s="23" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="I22" s="23" t="inlineStr"/>
-      <c r="J22" s="24" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="K22" s="24" t="inlineStr"/>
-      <c r="L22" s="25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="M22" s="25" t="inlineStr"/>
-      <c r="N22" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="26" t="inlineStr"/>
-      <c r="P22" s="27" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q22" s="27" t="inlineStr"/>
-      <c r="R22" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="n"/>
-      <c r="B23" s="21" t="n"/>
-      <c r="C23" s="21" t="n"/>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="22" t="inlineStr">
-        <is>
-          <t>SO1902</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G23" s="22" t="inlineStr"/>
-      <c r="H23" s="23" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="I23" s="23" t="inlineStr"/>
-      <c r="J23" s="24" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="K23" s="24" t="inlineStr"/>
-      <c r="L23" s="25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M23" s="25" t="inlineStr"/>
-      <c r="N23" s="26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O23" s="26" t="inlineStr"/>
-      <c r="P23" s="27" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="Q23" s="27" t="inlineStr"/>
-      <c r="R23" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="n"/>
-      <c r="B24" s="21" t="n"/>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>SO1903</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="inlineStr"/>
-      <c r="H24" s="23" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="I24" s="23" t="inlineStr"/>
-      <c r="J24" s="24" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="K24" s="24" t="inlineStr"/>
-      <c r="L24" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M24" s="25" t="inlineStr"/>
-      <c r="N24" s="26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O24" s="26" t="inlineStr"/>
-      <c r="P24" s="27" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="Q24" s="27" t="inlineStr"/>
-      <c r="R24" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="n"/>
-      <c r="B25" s="21" t="n"/>
-      <c r="C25" s="21" t="n"/>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="22" t="inlineStr">
-        <is>
-          <t>SO2001</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G25" s="22" t="inlineStr"/>
-      <c r="H25" s="23" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="I25" s="23" t="inlineStr"/>
-      <c r="J25" s="24" t="n">
-        <v>78</v>
-      </c>
-      <c r="K25" s="24" t="inlineStr"/>
-      <c r="L25" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="M25" s="25" t="inlineStr"/>
-      <c r="N25" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="26" t="inlineStr"/>
-      <c r="P25" s="27" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q25" s="27" t="inlineStr"/>
-      <c r="R25" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="21" t="n"/>
-      <c r="B26" s="21" t="n"/>
-      <c r="C26" s="21" t="n"/>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="22" t="inlineStr">
-        <is>
-          <t>SO2002</t>
-        </is>
-      </c>
-      <c r="F26" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G26" s="22" t="inlineStr"/>
-      <c r="H26" s="23" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="I26" s="23" t="inlineStr"/>
-      <c r="J26" s="24" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="K26" s="24" t="inlineStr"/>
-      <c r="L26" s="25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M26" s="25" t="inlineStr"/>
-      <c r="N26" s="26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O26" s="26" t="inlineStr"/>
-      <c r="P26" s="27" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="Q26" s="27" t="inlineStr"/>
-      <c r="R26" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="21" t="n"/>
-      <c r="B27" s="21" t="n"/>
-      <c r="C27" s="21" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="22" t="inlineStr">
-        <is>
-          <t>SO2003</t>
-        </is>
-      </c>
-      <c r="F27" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G27" s="22" t="inlineStr"/>
-      <c r="H27" s="23" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I27" s="23" t="inlineStr"/>
-      <c r="J27" s="24" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="K27" s="24" t="inlineStr"/>
-      <c r="L27" s="25" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="M27" s="25" t="inlineStr"/>
-      <c r="N27" s="26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O27" s="26" t="inlineStr"/>
-      <c r="P27" s="27" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="Q27" s="27" t="inlineStr"/>
-      <c r="R27" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="21" t="n"/>
-      <c r="B28" s="21" t="n"/>
-      <c r="C28" s="21" t="n"/>
-      <c r="D28" s="21" t="n"/>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>SO2101</t>
-        </is>
-      </c>
-      <c r="F28" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G28" s="22" t="inlineStr"/>
-      <c r="H28" s="23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I28" s="23" t="inlineStr"/>
-      <c r="J28" s="24" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="K28" s="24" t="inlineStr"/>
-      <c r="L28" s="25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M28" s="25" t="inlineStr"/>
-      <c r="N28" s="26" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O28" s="26" t="inlineStr"/>
-      <c r="P28" s="27" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="Q28" s="27" t="inlineStr"/>
-      <c r="R28" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="21" t="n"/>
-      <c r="B29" s="21" t="n"/>
-      <c r="C29" s="21" t="n"/>
-      <c r="D29" s="21" t="n"/>
-      <c r="E29" s="22" t="inlineStr">
-        <is>
-          <t>SO2203</t>
-        </is>
-      </c>
-      <c r="F29" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G29" s="22" t="inlineStr"/>
-      <c r="H29" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="I29" s="23" t="inlineStr"/>
-      <c r="J29" s="24" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="K29" s="24" t="inlineStr"/>
-      <c r="L29" s="25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M29" s="25" t="inlineStr"/>
-      <c r="N29" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="26" t="inlineStr"/>
-      <c r="P29" s="27" t="n">
-        <v>89</v>
-      </c>
-      <c r="Q29" s="27" t="inlineStr"/>
-      <c r="R29" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="21" t="n"/>
-      <c r="B30" s="21" t="n"/>
-      <c r="C30" s="21" t="n"/>
-      <c r="D30" s="21" t="n"/>
-      <c r="E30" s="22" t="inlineStr">
-        <is>
-          <t>SO2210</t>
-        </is>
-      </c>
-      <c r="F30" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G30" s="22" t="inlineStr"/>
-      <c r="H30" s="23" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="I30" s="23" t="inlineStr"/>
-      <c r="J30" s="24" t="n">
-        <v>88</v>
-      </c>
-      <c r="K30" s="24" t="inlineStr"/>
-      <c r="L30" s="25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M30" s="25" t="inlineStr"/>
-      <c r="N30" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="26" t="inlineStr"/>
-      <c r="P30" s="27" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="Q30" s="27" t="inlineStr"/>
-      <c r="R30" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="21" t="n"/>
-      <c r="B31" s="21" t="n"/>
-      <c r="C31" s="21" t="n"/>
-      <c r="D31" s="21" t="n"/>
-      <c r="E31" s="22" t="inlineStr">
-        <is>
-          <t>SO2301</t>
-        </is>
-      </c>
-      <c r="F31" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G31" s="22" t="inlineStr"/>
-      <c r="H31" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="23" t="inlineStr"/>
-      <c r="J31" s="24" t="n">
-        <v>100</v>
-      </c>
-      <c r="K31" s="24" t="inlineStr"/>
-      <c r="L31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="25" t="inlineStr"/>
-      <c r="N31" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="26" t="inlineStr"/>
-      <c r="P31" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q31" s="27" t="inlineStr"/>
-      <c r="R31" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="21" t="n"/>
-      <c r="B32" s="21" t="n"/>
-      <c r="C32" s="21" t="n"/>
-      <c r="D32" s="21" t="n"/>
-      <c r="E32" s="22" t="inlineStr">
-        <is>
-          <t>SO2302</t>
-        </is>
-      </c>
-      <c r="F32" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G32" s="22" t="inlineStr"/>
-      <c r="H32" s="23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I32" s="23" t="inlineStr"/>
-      <c r="J32" s="24" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="K32" s="24" t="inlineStr"/>
-      <c r="L32" s="25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M32" s="25" t="inlineStr"/>
-      <c r="N32" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="26" t="inlineStr"/>
-      <c r="P32" s="27" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="Q32" s="27" t="inlineStr"/>
-      <c r="R32" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="21" t="n"/>
-      <c r="B33" s="21" t="n"/>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="22" t="inlineStr">
-        <is>
-          <t>SO2401</t>
-        </is>
-      </c>
-      <c r="F33" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G33" s="22" t="inlineStr"/>
-      <c r="H33" s="23" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I33" s="23" t="inlineStr"/>
-      <c r="J33" s="24" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="K33" s="24" t="inlineStr"/>
-      <c r="L33" s="25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M33" s="25" t="inlineStr"/>
-      <c r="N33" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="26" t="inlineStr"/>
-      <c r="P33" s="27" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="Q33" s="27" t="inlineStr"/>
-      <c r="R33" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="21" t="n"/>
-      <c r="B34" s="21" t="n"/>
-      <c r="C34" s="21" t="n"/>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="22" t="inlineStr">
-        <is>
-          <t>SO2402</t>
-        </is>
-      </c>
-      <c r="F34" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G34" s="22" t="inlineStr"/>
-      <c r="H34" s="23" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I34" s="23" t="inlineStr"/>
-      <c r="J34" s="24" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="K34" s="24" t="inlineStr"/>
-      <c r="L34" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="25" t="inlineStr"/>
-      <c r="N34" s="26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O34" s="26" t="inlineStr"/>
-      <c r="P34" s="27" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="Q34" s="27" t="inlineStr"/>
-      <c r="R34" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="21" t="n"/>
-      <c r="B35" s="21" t="n"/>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="21" t="n"/>
-      <c r="E35" s="22" t="inlineStr">
-        <is>
-          <t>SO2403</t>
-        </is>
-      </c>
-      <c r="F35" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G35" s="22" t="inlineStr"/>
-      <c r="H35" s="23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I35" s="23" t="inlineStr"/>
-      <c r="J35" s="24" t="n">
-        <v>90</v>
-      </c>
-      <c r="K35" s="24" t="inlineStr"/>
-      <c r="L35" s="25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="M35" s="25" t="inlineStr"/>
-      <c r="N35" s="26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O35" s="26" t="inlineStr"/>
-      <c r="P35" s="27" t="n">
-        <v>96</v>
-      </c>
-      <c r="Q35" s="27" t="inlineStr"/>
-      <c r="R35" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="21" t="n"/>
-      <c r="B36" s="21" t="n"/>
-      <c r="C36" s="21" t="n"/>
-      <c r="D36" s="21" t="n"/>
-      <c r="E36" s="22" t="inlineStr">
-        <is>
-          <t>SO2404</t>
-        </is>
-      </c>
-      <c r="F36" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G36" s="22" t="inlineStr"/>
-      <c r="H36" s="23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="I36" s="23" t="inlineStr"/>
-      <c r="J36" s="24" t="n">
-        <v>67</v>
-      </c>
-      <c r="K36" s="24" t="inlineStr"/>
-      <c r="L36" s="25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="M36" s="25" t="inlineStr"/>
-      <c r="N36" s="26" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O36" s="26" t="inlineStr"/>
-      <c r="P36" s="27" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="Q36" s="27" t="inlineStr"/>
-      <c r="R36" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="21" t="n"/>
-      <c r="B37" s="21" t="n"/>
-      <c r="C37" s="21" t="n"/>
-      <c r="D37" s="21" t="n"/>
-      <c r="E37" s="22" t="inlineStr">
-        <is>
-          <t>SO2504</t>
-        </is>
-      </c>
-      <c r="F37" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G37" s="22" t="inlineStr"/>
-      <c r="H37" s="23" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="I37" s="23" t="inlineStr"/>
-      <c r="J37" s="24" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="K37" s="24" t="inlineStr"/>
-      <c r="L37" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="25" t="inlineStr"/>
-      <c r="N37" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="26" t="inlineStr"/>
-      <c r="P37" s="27" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="Q37" s="27" t="inlineStr"/>
-      <c r="R37" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="21" t="n"/>
-      <c r="B38" s="21" t="n"/>
-      <c r="C38" s="21" t="n"/>
-      <c r="D38" s="21" t="n"/>
-      <c r="E38" s="22" t="inlineStr">
-        <is>
-          <t>SO2602</t>
-        </is>
-      </c>
-      <c r="F38" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G38" s="22" t="inlineStr"/>
-      <c r="H38" s="23" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="I38" s="23" t="inlineStr"/>
-      <c r="J38" s="24" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="K38" s="24" t="inlineStr"/>
-      <c r="L38" s="25" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="M38" s="25" t="inlineStr"/>
-      <c r="N38" s="26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O38" s="26" t="inlineStr"/>
-      <c r="P38" s="27" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="Q38" s="27" t="inlineStr"/>
-      <c r="R38" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="21" t="n"/>
-      <c r="B39" s="21" t="n"/>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="21" t="n"/>
-      <c r="E39" s="22" t="inlineStr">
-        <is>
-          <t>SO2603</t>
-        </is>
-      </c>
-      <c r="F39" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G39" s="22" t="inlineStr"/>
-      <c r="H39" s="23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I39" s="23" t="inlineStr"/>
-      <c r="J39" s="24" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="K39" s="24" t="inlineStr"/>
-      <c r="L39" s="25" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="M39" s="25" t="inlineStr"/>
-      <c r="N39" s="26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O39" s="26" t="inlineStr"/>
-      <c r="P39" s="27" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="Q39" s="27" t="inlineStr"/>
-      <c r="R39" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="21" t="n"/>
-      <c r="B40" s="21" t="n"/>
-      <c r="C40" s="21" t="n"/>
-      <c r="D40" s="21" t="n"/>
-      <c r="E40" s="22" t="inlineStr">
-        <is>
-          <t>SO2604</t>
-        </is>
-      </c>
-      <c r="F40" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G40" s="22" t="inlineStr"/>
-      <c r="H40" s="23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I40" s="23" t="inlineStr"/>
-      <c r="J40" s="24" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="K40" s="24" t="inlineStr"/>
-      <c r="L40" s="25" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M40" s="25" t="inlineStr"/>
-      <c r="N40" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="26" t="inlineStr"/>
-      <c r="P40" s="27" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="Q40" s="27" t="inlineStr"/>
-      <c r="R40" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="21" t="n"/>
-      <c r="B41" s="21" t="n"/>
-      <c r="C41" s="21" t="n"/>
-      <c r="D41" s="21" t="n"/>
-      <c r="E41" s="22" t="inlineStr">
-        <is>
-          <t>SO2605</t>
-        </is>
-      </c>
-      <c r="F41" s="22" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G41" s="22" t="inlineStr"/>
-      <c r="H41" s="23" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="I41" s="23" t="inlineStr"/>
-      <c r="J41" s="24" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="K41" s="24" t="inlineStr"/>
-      <c r="L41" s="25" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="M41" s="25" t="inlineStr"/>
-      <c r="N41" s="26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O41" s="26" t="inlineStr"/>
-      <c r="P41" s="27" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="Q41" s="27" t="inlineStr"/>
-      <c r="R41" s="28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="21" t="n"/>
-      <c r="B42" s="21" t="n"/>
-      <c r="C42" s="21" t="n"/>
-      <c r="D42" s="21" t="n"/>
-      <c r="E42" s="29" t="inlineStr">
-        <is>
-          <t>SO2606</t>
-        </is>
-      </c>
-      <c r="F42" s="29" t="inlineStr">
-        <is>
-          <t>recent_idp</t>
-        </is>
-      </c>
-      <c r="G42" s="29" t="inlineStr"/>
-      <c r="H42" s="30" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="I42" s="30" t="inlineStr"/>
-      <c r="J42" s="31" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="K42" s="31" t="inlineStr"/>
-      <c r="L42" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="M42" s="32" t="inlineStr"/>
-      <c r="N42" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="33" t="inlineStr"/>
-      <c r="P42" s="34" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="Q42" s="34" t="inlineStr"/>
-      <c r="R42" s="28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="E1:R1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>